--- a/docs/source/Valuation Dashboard.xlsx
+++ b/docs/source/Valuation Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEF Esma\Downloads\Michelscom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCF941F-8F41-47C6-BCCE-049A9D52DB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12AD185-5BD6-4115-BC62-9FC73244B9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Valuation" sheetId="2" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="Comparable Companies&gt;&gt;&gt;" sheetId="6" r:id="rId5"/>
     <sheet name="Companies" sheetId="7" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="513">
   <si>
     <t>Comparable Companies</t>
   </si>
@@ -1312,15 +1309,9 @@
     <t>http://haysplc.com</t>
   </si>
   <si>
-    <t>Brunel is a recruitment agency specializing in workforce solutions across various industries including Conventional Energy, Mining, and Life Sciences. The company connects skilled professionals with businesses seeking talent, offering services such as contract hire, direct hire, and consulting solutions. Brunel operates globally, providing tailored support to enhance operational efficiency for its clients.</t>
-  </si>
-  <si>
     <t>Netherlands</t>
   </si>
   <si>
-    <t>http://brunel.net</t>
-  </si>
-  <si>
     <t>NGS Group</t>
   </si>
   <si>
@@ -1393,52 +1384,202 @@
     <t>http://empresaria.com</t>
   </si>
   <si>
-    <t>Gattaca</t>
-  </si>
-  <si>
-    <t>Gattaca PLC is a recruitment agency specializing in STEM sectors, providing talent solutions for engineering and technology companies. They help businesses tackle workforce challenges by connecting them with skilled professionals. Gattaca operates in various industries, including aerospace and energy, and focuses on delivering project management and consulting services to meet client needs.</t>
-  </si>
-  <si>
-    <t>http://gattacaplc.com</t>
-  </si>
-  <si>
-    <t>Freelance.com</t>
-  </si>
-  <si>
-    <t>Freelance.com is a talent management service that connects businesses with freelancers and small to medium enterprises. It offers solutions for sourcing talent, managing payroll, and providing administrative support, catering to the needs of organizations seeking flexible workforce solutions. The company operates a digital platform that facilitates project management and training services for its users.</t>
-  </si>
-  <si>
-    <t>http://freelance.com</t>
-  </si>
-  <si>
-    <t>RTC Group Plc</t>
-  </si>
-  <si>
-    <t>RTC Group Plc is a recruitment agency that specializes in providing staffing solutions for both white and blue-collar positions across various sectors, including engineering, construction, and transportation. The company operates through its brands, such as ATA Recruitment and Ganymede, to deliver tailored recruitment services to businesses and organizations in need of qualified personnel.</t>
-  </si>
-  <si>
-    <t>http://rtcgroupplc.co.uk</t>
-  </si>
-  <si>
-    <t>SThree</t>
-  </si>
-  <si>
-    <t>SThree is a consultancy specializing in STEM workforce solutions, connecting skilled professionals with organizations in need of expertise in science, technology, engineering, and mathematics. The company operates through various specialist brands, providing recruitment and strategic consulting services to businesses across multiple sectors, including life sciences and financial services.</t>
-  </si>
-  <si>
-    <t>http://sthree.com</t>
-  </si>
-  <si>
-    <t>Additional Transactions</t>
-  </si>
-  <si>
-    <t>Main Comparable Transactions</t>
-  </si>
-  <si>
-    <t>Main Comparable Companies</t>
-  </si>
-  <si>
-    <t>Additional Comparable Companies</t>
+    <t>Hitechpros</t>
+  </si>
+  <si>
+    <t>HiTechPros is an IT staffing platform that connects IT professionals with businesses, offering a range of services including staffing solutions, training, and consulting. The company serves a diverse clientele, including freelancers, training centers, and software publishers, facilitating access to numerous opportunities in the IT sector. HiTechPros operates a digital platform that enhances collaboration and sourcing in the IT community.</t>
+  </si>
+  <si>
+    <t>http://hitechpros.com</t>
+  </si>
+  <si>
+    <t>Korn Ferry</t>
+  </si>
+  <si>
+    <t>Korn Ferry is a consulting firm specializing in organizational consulting services. They offer a range of solutions including talent acquisition, leadership development, and organizational strategy to help businesses and organizations enhance their performance and manage talent effectively. Their clients span various industries, seeking to navigate complex challenges and drive growth.</t>
+  </si>
+  <si>
+    <t>United States (USA)</t>
+  </si>
+  <si>
+    <t>http://kornferry.com</t>
+  </si>
+  <si>
+    <t>Insight Global</t>
+  </si>
+  <si>
+    <t>Insight Global is a staffing agency and consulting firm that specializes in providing staffing and professional services across various industries. They assist businesses in finding qualified talent and offer solutions to improve operational efficiency. Their services include staffing, recruitment process outsourcing, and culture consulting, catering primarily to business clients.</t>
+  </si>
+  <si>
+    <t>http://insightglobal.com</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>EV/Sales Historical EV 2021</t>
+  </si>
+  <si>
+    <t>EV/Sales Historical EV 2022</t>
+  </si>
+  <si>
+    <t>ATOSS Software SE</t>
+  </si>
+  <si>
+    <t>ATOSS Software SE is a workforce management solutions provider that specializes in software for time tracking, personnel planning, and HR analytics. Their offerings cater to businesses in various sectors, helping them enhance productivity and employee satisfaction through innovative technology and consulting services. ATOSS operates primarily in the cloud, ensuring flexibility and compliance for its clients.</t>
+  </si>
+  <si>
+    <t>http://atoss.com</t>
+  </si>
+  <si>
+    <t>Calviks AB is an investment company focused on competence supply and development of niche firms. It operates in Sweden, Norway, and Denmark, providing recruitment, consulting, and staffing services to businesses in various sectors. The company aims to enhance organizational efficiency by connecting clients with specialized talent and expertise.</t>
+  </si>
+  <si>
+    <t>http://calviks.se</t>
+  </si>
+  <si>
+    <t>Dedicare AB</t>
+  </si>
+  <si>
+    <t>Dedicare is a staffing agency specializing in recruitment for the healthcare, life science, and social work sectors. The company connects qualified professionals with organizations in need of temporary or permanent staff, ensuring that healthcare providers can maintain high-quality services. Dedicare operates across various regions, offering both local and international staffing solutions.</t>
+  </si>
+  <si>
+    <t>http://dedicare.se</t>
+  </si>
+  <si>
+    <t>Norman Broadbent Plc</t>
+  </si>
+  <si>
+    <t>Norman Broadbent PLC is an executive search firm specializing in leadership solutions. The company offers services such as board search, executive search, interim management, and leadership development to businesses across various sectors, including consumer markets and financial services. Their clients range from SMEs to large corporations seeking to enhance their leadership capabilities. Norman Broadbent operates from multiple locations in the UK.</t>
+  </si>
+  <si>
+    <t>http://normanbroadbent.com</t>
+  </si>
+  <si>
+    <t>CRIT France</t>
+  </si>
+  <si>
+    <t>Groupe CRIT is a staffing agency and airport services provider that specializes in temporary staffing and recruitment, as well as airport assistance. They serve a diverse clientele, including over 38,000 companies, by offering flexible workforce solutions and operational support in various industries. The company operates internationally, with a strong presence in France and several other countries.</t>
+  </si>
+  <si>
+    <t>http://groupe-crit.com</t>
+  </si>
+  <si>
+    <t>Digital Workforce Services Plc</t>
+  </si>
+  <si>
+    <t>Digital Workforce Services Plc is a business process automation company that offers a comprehensive suite of automation services and technology solutions. They cater to various industries, helping organizations enhance operational efficiency, reduce costs, and improve customer experiences through intelligent automation. Their services include RPA, AI agents, and process redesign, targeting businesses in sectors like healthcare and banking.</t>
+  </si>
+  <si>
+    <t>http://digitalworkforce.com</t>
+  </si>
+  <si>
+    <t>ad pepper Group</t>
+  </si>
+  <si>
+    <t>ad pepper media International N.V. is a digital marketing agency specializing in performance marketing and affiliate marketing. The company offers a range of services designed to help businesses enhance their online presence and sales through innovative marketing strategies. With a focus on measurable and transparent results, ad pepper media serves a diverse clientele, including startups and established global brands.</t>
+  </si>
+  <si>
+    <t>http://adpeppergroup.com</t>
+  </si>
+  <si>
+    <t>Alma Media</t>
+  </si>
+  <si>
+    <t>Alma Media is a media company that provides a range of digital services including recruitment, real estate, and automotive solutions. It serves both businesses and consumers, leveraging its extensive media reach to facilitate transactions and enhance customer experiences. The company operates through various digital platforms, focusing on creating value through innovative services and technology.</t>
+  </si>
+  <si>
+    <t>http://almamedia.fi</t>
+  </si>
+  <si>
+    <t>PERBILITY GmbH</t>
+  </si>
+  <si>
+    <t>HR SaaS / HRIS</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Rivean Capital ← Main Capital</t>
+  </si>
+  <si>
+    <t>⭐⭐German HRIS/HR SaaS, 147 employees, DACH-focused PE LBO — strongest German comp with full multiples</t>
+  </si>
+  <si>
+    <t>PandoLogic</t>
+  </si>
+  <si>
+    <t>AI Recruitment Marketing</t>
+  </si>
+  <si>
+    <t>Veritone ← Edison Partners</t>
+  </si>
+  <si>
+    <t>⭐⭐AI-powered recruitment marketing platform — directly aligned with Michelscom's tech-enabled positioning</t>
+  </si>
+  <si>
+    <t>1st Quartile</t>
+  </si>
+  <si>
+    <t>3rd Quartile</t>
+  </si>
+  <si>
+    <t>Optional - Additional Transactions</t>
+  </si>
+  <si>
+    <t>Payroll / HR Software</t>
+  </si>
+  <si>
+    <t>10.4x</t>
+  </si>
+  <si>
+    <t>18.5x</t>
+  </si>
+  <si>
+    <t>12.3x</t>
+  </si>
+  <si>
+    <t>Apax ← Bain Capital</t>
+  </si>
+  <si>
+    <t>⭐UK payroll &amp; HR SaaS — large PE-to-PE deal; illustrates software multiple premium vs. agency</t>
+  </si>
+  <si>
+    <t>Zalaris</t>
+  </si>
+  <si>
+    <t>HR &amp; Payroll SaaS</t>
+  </si>
+  <si>
+    <t>1.8x</t>
+  </si>
+  <si>
+    <t>Kona BidCo</t>
+  </si>
+  <si>
+    <t>⭐Nordic HR &amp; payroll SaaS take-private — EV/Sales useful for comparing services-heavy SaaS</t>
+  </si>
+  <si>
+    <t>Darwinbox</t>
+  </si>
+  <si>
+    <t>🇮🇳 IN</t>
+  </si>
+  <si>
+    <t>HR Tech Unicorn</t>
+  </si>
+  <si>
+    <t>3.0x</t>
+  </si>
+  <si>
+    <t>KKR, Partners Group</t>
+  </si>
+  <si>
+    <t>⭐High-growth HR tech platform; EV/Sales reference for growth-stage HR software at scale</t>
+  </si>
+  <si>
+    <t>Sources: Inven transaction database · tsv_T2d9dz7hRD, tsv_BZzW1WsXYL (HR Tech / HR Services searches, 2021–2026) · ⭐⭐⭐ = direct DACH peer &amp; closest profile match · ⭐⭐ = directly comparable European recruiting/HR agency with disclosed multiples · ⭐ = broader HR-tech sector benchmark · All amounts in USD millions · N/D = not disclosed</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1592,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1541,12 +1682,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF1464C8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF7E7A77"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1565,8 +1700,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF201E1C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF201E1C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0E3270"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1464C8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB0ADA9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1606,6 +1772,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1649,7 +1821,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1753,29 +1925,72 @@
     <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1792,118 +2007,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Valuation"/>
-      <sheetName val="Precedent Transactions&gt;&gt;&gt;"/>
-      <sheetName val="Transactions"/>
-      <sheetName val="Relevant Transactions"/>
-      <sheetName val="Comparable Companies&gt;&gt;&gt;"/>
-      <sheetName val="Companies"/>
-      <sheetName val="Comps Multiple Trend"/>
-      <sheetName val="Buyer Universe&gt;&gt;&gt;"/>
-      <sheetName val="Strategic Buyers"/>
-      <sheetName val="Financial Sponsors"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6">
-        <row r="18">
-          <cell r="C18">
-            <v>2021</v>
-          </cell>
-          <cell r="D18">
-            <v>2022</v>
-          </cell>
-          <cell r="E18">
-            <v>2023</v>
-          </cell>
-          <cell r="F18">
-            <v>2024</v>
-          </cell>
-          <cell r="G18">
-            <v>2025</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>EV/Revenue</v>
-          </cell>
-          <cell r="C19">
-            <v>1.9829916666666669</v>
-          </cell>
-          <cell r="D19">
-            <v>1.0298</v>
-          </cell>
-          <cell r="E19">
-            <v>1.0244000000000002</v>
-          </cell>
-          <cell r="F19">
-            <v>0.86007692307692296</v>
-          </cell>
-          <cell r="G19">
-            <v>0.70723076923076933</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>EV/EBITDA</v>
-          </cell>
-          <cell r="C20">
-            <v>12.376276923076924</v>
-          </cell>
-          <cell r="D20">
-            <v>8.5398230769230778</v>
-          </cell>
-          <cell r="E20">
-            <v>7.808923076923076</v>
-          </cell>
-          <cell r="F20">
-            <v>9.1334384615384625</v>
-          </cell>
-          <cell r="G20">
-            <v>10.851938461538461</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>EV/EBIT</v>
-          </cell>
-          <cell r="C21">
-            <v>15.702184615384615</v>
-          </cell>
-          <cell r="D21">
-            <v>11.434376923076922</v>
-          </cell>
-          <cell r="E21">
-            <v>12.038338461538462</v>
-          </cell>
-          <cell r="F21">
-            <v>17.542938461538462</v>
-          </cell>
-          <cell r="G21">
-            <v>18.320430769230772</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2221,19 +2324,19 @@
       </c>
       <c r="C7" s="3">
         <f>Companies!S19</f>
-        <v>7.024</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3">
         <f>Companies!S20</f>
-        <v>9.3032000000000004</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <f>Companies!S22</f>
-        <v>10.822171428571426</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
         <f>Companies!S21</f>
-        <v>18.777100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
@@ -2242,19 +2345,19 @@
       </c>
       <c r="C8" s="5">
         <f>C6*C7</f>
-        <v>18.40288</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5">
         <f t="shared" ref="D8:F8" si="0">D6*D7</f>
-        <v>24.374384000000003</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5">
         <f t="shared" si="0"/>
-        <v>28.354089142857138</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>49.196002000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.55000000000000004">
@@ -2302,19 +2405,19 @@
       </c>
       <c r="C14" s="3">
         <f>'Relevant Transactions'!I15</f>
-        <v>8.1</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="D14" s="3">
         <f>'Relevant Transactions'!I16</f>
-        <v>9.0500000000000007</v>
+        <v>10.175000000000001</v>
       </c>
       <c r="E14" s="3">
         <f>'Relevant Transactions'!I18</f>
-        <v>10.833333333333334</v>
+        <v>18.7</v>
       </c>
       <c r="F14" s="3">
         <f>'Relevant Transactions'!I17</f>
-        <v>18.7</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
@@ -2323,19 +2426,19 @@
       </c>
       <c r="C15" s="5">
         <f>C13*C14</f>
-        <v>21.222000000000001</v>
+        <v>23.711000000000002</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" ref="D15:F15" si="1">D13*D14</f>
-        <v>23.711000000000002</v>
+        <v>26.658500000000004</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>28.383333333333336</v>
+        <v>48.994</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>48.994</v>
+        <v>28.296000000000003</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.55000000000000004">
@@ -4802,13 +4905,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15118375-713A-4FE6-A464-574B191A541D}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B3:L29"/>
+  <dimension ref="B3:M33"/>
   <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="25"/>
     <col min="2" max="2" width="19.578125" style="25" customWidth="1"/>
     <col min="3" max="3" width="8" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.20703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.68359375" style="25" customWidth="1"/>
     <col min="5" max="5" width="8.83984375" style="25"/>
     <col min="6" max="6" width="14.734375" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.9453125" style="25" bestFit="1" customWidth="1"/>
@@ -4816,268 +4919,323 @@
     <col min="9" max="9" width="9.83984375" style="25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.41796875" style="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.68359375" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.83984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.83984375" style="66" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="8.83984375" style="25"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.5">
       <c r="B3" s="23" t="s">
-        <v>462</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.5">
-      <c r="B4" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D3" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E3" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F3" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G3" s="24" t="s">
         <v>308</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H3" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J3" s="24" t="s">
         <v>310</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K3" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="L3" s="65" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="61.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:12" ht="61.5" x14ac:dyDescent="0.5">
+      <c r="B5" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="D5" s="28">
+        <v>46082</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="30">
+        <v>100</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="H5" s="30">
+        <v>2.7</v>
+      </c>
+      <c r="I5" s="30">
+        <v>12</v>
+      </c>
+      <c r="J5" s="30">
+        <v>7.4</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
       <c r="B6" s="26" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D6" s="28">
-        <v>46082</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>315</v>
+        <v>45962</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>320</v>
       </c>
       <c r="F6" s="30">
-        <v>100</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>316</v>
+        <v>12.9</v>
+      </c>
+      <c r="G6" s="30">
+        <v>13.1</v>
       </c>
       <c r="H6" s="30">
-        <v>2.7</v>
+        <v>12.9</v>
       </c>
       <c r="I6" s="30">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="J6" s="30">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>47</v>
+        <v>321</v>
       </c>
       <c r="L6" s="27" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
       <c r="B7" s="26" t="s">
-        <v>318</v>
+        <v>93</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D7" s="28">
-        <v>45962</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>320</v>
+        <v>45748</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>323</v>
       </c>
       <c r="F7" s="30">
-        <v>12.9</v>
-      </c>
-      <c r="G7" s="30">
-        <v>13.1</v>
+        <v>29.8</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>316</v>
       </c>
       <c r="H7" s="30">
-        <v>12.9</v>
+        <v>0.1</v>
       </c>
       <c r="I7" s="30">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="J7" s="30">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
       <c r="B8" s="26" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>314</v>
       </c>
       <c r="D8" s="28">
-        <v>45748</v>
+        <v>45200</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F8" s="30">
-        <v>29.8</v>
+        <v>16.5</v>
       </c>
       <c r="G8" s="30" t="s">
         <v>316</v>
       </c>
       <c r="H8" s="30">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="I8" s="30">
         <v>8.1</v>
       </c>
       <c r="J8" s="30">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L8" s="27" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="61.5" x14ac:dyDescent="0.5">
       <c r="B9" s="26" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="D9" s="28">
-        <v>45200</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>326</v>
+        <v>45139</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>330</v>
       </c>
       <c r="F9" s="30">
-        <v>16.5</v>
-      </c>
-      <c r="G9" s="30" t="s">
+        <v>440</v>
+      </c>
+      <c r="G9" s="34">
+        <v>1947</v>
+      </c>
+      <c r="H9" s="30">
+        <v>5.6</v>
+      </c>
+      <c r="I9" s="30">
+        <v>18.7</v>
+      </c>
+      <c r="J9" s="30">
+        <v>18.8</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
+      <c r="B10" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="D10" s="28">
+        <v>45078</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="F10" s="30">
+        <v>52</v>
+      </c>
+      <c r="G10" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="H9" s="30">
-        <v>0.6</v>
-      </c>
-      <c r="I9" s="30">
-        <v>8.1</v>
-      </c>
-      <c r="J9" s="30">
-        <v>8.1</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="61.5" x14ac:dyDescent="0.5">
-      <c r="B10" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>329</v>
-      </c>
-      <c r="D10" s="28">
-        <v>45139</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="F10" s="30">
-        <v>440</v>
-      </c>
-      <c r="G10" s="34">
-        <v>1947</v>
-      </c>
       <c r="H10" s="30">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="I10" s="30">
-        <v>18.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J10" s="30">
-        <v>18.8</v>
+        <v>6.1</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="L10" s="27" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
-      <c r="B11" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="27" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="82.8" x14ac:dyDescent="0.5">
+      <c r="B11" s="67" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>355</v>
+      </c>
+      <c r="D11" s="69">
+        <v>45566</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>484</v>
+      </c>
+      <c r="F11" s="71">
+        <v>110</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="H11" s="30">
+        <v>3.3</v>
+      </c>
+      <c r="I11" s="30">
+        <v>10.4</v>
+      </c>
+      <c r="J11" s="30">
+        <v>9.9</v>
+      </c>
+      <c r="K11" s="68" t="s">
+        <v>486</v>
+      </c>
+      <c r="L11" s="68" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="82.8" x14ac:dyDescent="0.5">
+      <c r="B12" s="67" t="s">
+        <v>488</v>
+      </c>
+      <c r="C12" s="68" t="s">
         <v>333</v>
       </c>
-      <c r="D11" s="28">
-        <v>45078</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="F11" s="30">
-        <v>52</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="H11" s="30">
-        <v>2.1</v>
-      </c>
-      <c r="I11" s="30">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J11" s="30">
-        <v>6.1</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>336</v>
+      <c r="D12" s="69">
+        <v>44378</v>
+      </c>
+      <c r="E12" s="70" t="s">
+        <v>489</v>
+      </c>
+      <c r="F12" s="71">
+        <v>150</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="H12" s="30">
+        <v>3</v>
+      </c>
+      <c r="I12" s="30">
+        <v>6</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="K12" s="68" t="s">
+        <v>490</v>
+      </c>
+      <c r="L12" s="68" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.5">
@@ -5094,45 +5252,56 @@
       <c r="L13" s="27"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.5">
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="27"/>
+      <c r="B14" s="35" t="s">
+        <v>492</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="73">
+        <f>QUARTILE(H4:H12,1)</f>
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="I14" s="73">
+        <f>QUARTILE(I4:I12,1)</f>
+        <v>8.1</v>
+      </c>
+      <c r="J14" s="73">
+        <f>QUARTILE(J4:J12,1)</f>
+        <v>6.75</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="36"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.5">
       <c r="B15" s="35" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="36"/>
       <c r="D15" s="37"/>
       <c r="E15" s="38"/>
       <c r="F15" s="39"/>
       <c r="G15" s="40"/>
-      <c r="H15" s="40">
-        <f>MIN(H5:H12)</f>
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="40">
-        <f>MIN(I5:I12)</f>
+      <c r="H15" s="42">
+        <f>MEDIAN(H4:H12)</f>
+        <v>2.85</v>
+      </c>
+      <c r="I15" s="42">
+        <f>MEDIAN(I4:I12)</f>
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="J15" s="42">
+        <f>MEDIAN(J4:J12)</f>
         <v>8.1</v>
-      </c>
-      <c r="J15" s="40">
-        <f>MIN(J5:J12)</f>
-        <v>5.9</v>
       </c>
       <c r="K15" s="41"/>
       <c r="L15" s="36"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.5">
       <c r="B16" s="35" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="36"/>
       <c r="D16" s="37"/>
@@ -5140,110 +5309,123 @@
       <c r="F16" s="39"/>
       <c r="G16" s="40"/>
       <c r="H16" s="42">
-        <f>MEDIAN(H5:H12)</f>
-        <v>2.4000000000000004</v>
+        <f>AVERAGE(H4:H12)</f>
+        <v>3.7875000000000001</v>
       </c>
       <c r="I16" s="42">
-        <f>MEDIAN(I5:I12)</f>
-        <v>9.0500000000000007</v>
+        <f>AVERAGE(I4:I12)</f>
+        <v>10.175000000000001</v>
       </c>
       <c r="J16" s="42">
-        <f>MEDIAN(J5:J12)</f>
-        <v>7.75</v>
+        <f>AVERAGE(J4:J12)</f>
+        <v>9.3285714285714274</v>
       </c>
       <c r="K16" s="41"/>
       <c r="L16" s="36"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.5">
       <c r="B17" s="35" t="s">
-        <v>5</v>
+        <v>493</v>
       </c>
       <c r="C17" s="36"/>
       <c r="D17" s="37"/>
       <c r="E17" s="38"/>
       <c r="F17" s="39"/>
       <c r="G17" s="40"/>
-      <c r="H17" s="40">
-        <f>MAX(H5:H12)</f>
-        <v>12.9</v>
-      </c>
-      <c r="I17" s="40">
-        <f>MAX(I5:I12)</f>
-        <v>18.7</v>
-      </c>
-      <c r="J17" s="40">
-        <f>MAX(J5:J12)</f>
-        <v>18.8</v>
+      <c r="H17" s="73">
+        <f>QUARTILE(H4:H12,3)</f>
+        <v>3.875</v>
+      </c>
+      <c r="I17" s="73">
+        <f>QUARTILE(I4:I12,3)</f>
+        <v>10.8</v>
+      </c>
+      <c r="J17" s="73">
+        <f>QUARTILE(J4:J12,3)</f>
+        <v>9.5</v>
       </c>
       <c r="K17" s="41"/>
       <c r="L17" s="36"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.5">
       <c r="B18" s="35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="36"/>
       <c r="D18" s="37"/>
       <c r="E18" s="38"/>
       <c r="F18" s="39"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="42">
-        <f>AVERAGE(H5:H12)</f>
-        <v>4</v>
-      </c>
-      <c r="I18" s="42">
-        <f>AVERAGE(I5:I12)</f>
-        <v>10.833333333333334</v>
-      </c>
-      <c r="J18" s="42">
-        <f>AVERAGE(J5:J12)</f>
-        <v>9.2333333333333325</v>
+      <c r="H18" s="73">
+        <f>MAX(H4:H12)</f>
+        <v>12.9</v>
+      </c>
+      <c r="I18" s="73">
+        <f>MAX(I4:I12)</f>
+        <v>18.7</v>
+      </c>
+      <c r="J18" s="73">
+        <f>MAX(J4:J12)</f>
+        <v>18.8</v>
       </c>
       <c r="K18" s="41"/>
       <c r="L18" s="36"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.5">
-      <c r="B19" s="26"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-    </row>
-    <row r="20" spans="2:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="46" t="s">
+      <c r="B19" s="52" t="s">
         <v>337</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-    </row>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+    </row>
+    <row r="20" spans="2:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.5"/>
     <row r="21" spans="2:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="23" t="s">
-        <v>461</v>
-      </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
+      <c r="B21" s="25" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B22" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="L22" s="65" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="23" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
       <c r="B23" s="26" t="s">
@@ -5255,7 +5437,7 @@
       <c r="D23" s="28">
         <v>45597</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="43" t="s">
         <v>339</v>
       </c>
       <c r="F23" s="30">
@@ -5395,7 +5577,7 @@
       <c r="D27" s="28">
         <v>45901</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="43" t="s">
         <v>356</v>
       </c>
       <c r="F27" s="30" t="s">
@@ -5430,7 +5612,7 @@
       <c r="D28" s="28">
         <v>45261</v>
       </c>
-      <c r="E28" s="47" t="s">
+      <c r="E28" s="43" t="s">
         <v>360</v>
       </c>
       <c r="F28" s="30" t="s">
@@ -5490,9 +5672,131 @@
         <v>366</v>
       </c>
     </row>
+    <row r="30" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
+      <c r="B30" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="D30" s="28">
+        <v>45383</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>495</v>
+      </c>
+      <c r="F30" s="30">
+        <v>1587</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="I30" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>498</v>
+      </c>
+      <c r="K30" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="L30" s="27" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="61.5" x14ac:dyDescent="0.5">
+      <c r="B31" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="D31" s="28">
+        <v>46113</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>502</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="G31" s="30">
+        <v>206</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>503</v>
+      </c>
+      <c r="I31" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="J31" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="K31" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="49.2" x14ac:dyDescent="0.5">
+      <c r="B32" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>507</v>
+      </c>
+      <c r="D32" s="28">
+        <v>45717</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="F32" s="30">
+        <v>140</v>
+      </c>
+      <c r="G32" s="30">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="I32" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="J32" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="K32" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="L32" s="27" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.5">
+      <c r="B33" s="74" t="s">
+        <v>512</v>
+      </c>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="74"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B20:L20"/>
+  <mergeCells count="2">
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="B33:M33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5516,7 +5820,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7DC679-9428-488D-8EAA-2D987579F20D}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="B2:AA31"/>
+  <dimension ref="B2:Y40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.734375" customWidth="1"/>
@@ -5527,1802 +5831,2235 @@
     <col min="7" max="8" width="14.734375" customWidth="1"/>
     <col min="9" max="9" width="22.15625" customWidth="1"/>
     <col min="10" max="11" width="14.734375" customWidth="1"/>
-    <col min="12" max="15" width="22.15625" customWidth="1"/>
+    <col min="12" max="12" width="22.15625" style="62" customWidth="1"/>
+    <col min="13" max="15" width="22.15625" customWidth="1"/>
     <col min="16" max="16" width="14.734375" customWidth="1"/>
     <col min="17" max="17" width="22.15625" customWidth="1"/>
     <col min="18" max="18" width="14.734375" customWidth="1"/>
     <col min="19" max="19" width="18.15625" customWidth="1"/>
     <col min="20" max="20" width="26.20703125" customWidth="1"/>
-    <col min="21" max="21" width="33.62890625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.62890625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="14.734375" customWidth="1"/>
     <col min="23" max="23" width="18.9453125" customWidth="1"/>
     <col min="24" max="24" width="32.62890625" customWidth="1"/>
     <col min="25" max="27" width="14.734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="L2" s="53" t="s">
+        <v>376</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>377</v>
+      </c>
+      <c r="N2" s="44" t="s">
+        <v>378</v>
+      </c>
+      <c r="O2" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="P2" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q2" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="R2" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="S2" s="44" t="s">
+        <v>383</v>
+      </c>
+      <c r="T2" s="44" t="s">
+        <v>384</v>
+      </c>
+      <c r="U2" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="V2" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="W2" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="X2" s="44" t="s">
+        <v>388</v>
+      </c>
+      <c r="Y2" s="44" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="45">
+        <v>11028540</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>391</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>392</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>393</v>
+      </c>
+      <c r="G3" s="47">
+        <v>590</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I3" s="47">
+        <v>216.1122048</v>
+      </c>
+      <c r="J3" s="48">
+        <v>0.1005670513875327</v>
+      </c>
+      <c r="K3" s="47">
+        <f>M3*Q3</f>
+        <v>859.42735012224</v>
+      </c>
+      <c r="L3" s="54">
+        <v>216.1122048</v>
+      </c>
+      <c r="M3" s="47">
+        <v>97.524777599999993</v>
+      </c>
+      <c r="N3" s="48">
+        <v>0.45126918070293082</v>
+      </c>
+      <c r="O3" s="47">
+        <v>97.524777599999993</v>
+      </c>
+      <c r="P3" s="49">
+        <v>3.9767999999999999</v>
+      </c>
+      <c r="Q3" s="49">
+        <v>8.8124000000000002</v>
+      </c>
+      <c r="R3" s="49">
+        <v>9.9036000000000008</v>
+      </c>
+      <c r="S3" s="48">
+        <v>2.1822889132818268E-2</v>
+      </c>
+      <c r="T3" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U3" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V3" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W3" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="45">
+        <v>5280480</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>399</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="G4" s="47">
+        <v>1135</v>
+      </c>
+      <c r="H4" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I4" s="47">
+        <v>414.85669200000001</v>
+      </c>
+      <c r="J4" s="48">
+        <v>-3.6945463803843233E-2</v>
+      </c>
+      <c r="K4" s="47">
+        <f>M4*Q4</f>
+        <v>429.38360761274998</v>
+      </c>
+      <c r="L4" s="54">
+        <v>414.85669200000001</v>
+      </c>
+      <c r="M4" s="47">
+        <v>49.033185750000001</v>
+      </c>
+      <c r="N4" s="48">
+        <v>0.1181930693069307</v>
+      </c>
+      <c r="O4" s="47">
+        <v>49.033185750000001</v>
+      </c>
+      <c r="P4" s="49">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="Q4" s="49">
+        <v>8.7569999999999997</v>
+      </c>
+      <c r="R4" s="49">
+        <v>30.8672</v>
+      </c>
+      <c r="S4" s="48">
+        <v>3.3556562757084192E-2</v>
+      </c>
+      <c r="T4" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U4" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V4" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W4" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="45"/>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="45">
+        <v>18285512</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>403</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>404</v>
+      </c>
+      <c r="G5" s="47">
+        <v>666</v>
+      </c>
+      <c r="H5" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I5" s="47">
+        <v>158.97705495</v>
+      </c>
+      <c r="J5" s="48">
+        <v>-0.1743952190243411</v>
+      </c>
+      <c r="K5" s="47">
+        <f>M5*Q5</f>
+        <v>74.010890240799995</v>
+      </c>
+      <c r="L5" s="54">
+        <v>158.97705495</v>
+      </c>
+      <c r="M5" s="47">
+        <v>10.53685795</v>
+      </c>
+      <c r="N5" s="48">
+        <v>6.6279111493881659E-2</v>
+      </c>
+      <c r="O5" s="47">
+        <v>10.53685795</v>
+      </c>
+      <c r="P5" s="49">
+        <v>0.46550000000000002</v>
+      </c>
+      <c r="Q5" s="49">
+        <v>7.024</v>
+      </c>
+      <c r="R5" s="49">
+        <v>175.791</v>
+      </c>
+      <c r="S5" s="48">
+        <v>0.15610954377561809</v>
+      </c>
+      <c r="T5" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U5" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V5" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W5" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="45">
+        <v>501430</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>405</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>406</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="G6" s="47">
+        <v>4145</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I6" s="47">
+        <v>234.92665768000001</v>
+      </c>
+      <c r="J6" s="48">
+        <v>-0.18637283467358781</v>
+      </c>
+      <c r="K6" s="47">
+        <f>M6*Q6</f>
+        <v>173.627679657952</v>
+      </c>
+      <c r="L6" s="54">
+        <f>I6</f>
+        <v>234.92665768000001</v>
+      </c>
+      <c r="M6" s="47">
+        <v>24.179097280000001</v>
+      </c>
+      <c r="N6" s="48">
+        <v>0.1029218970668497</v>
+      </c>
+      <c r="O6" s="47">
+        <v>24.179097280000001</v>
+      </c>
+      <c r="P6" s="49">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7.1809000000000003</v>
+      </c>
+      <c r="R6" s="49">
+        <v>9.9667999999999992</v>
+      </c>
+      <c r="S6" s="48">
+        <v>-0.14732004381615971</v>
+      </c>
+      <c r="T6" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U6" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V6" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W6" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="45">
+        <v>5174553</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="G7" s="47">
+        <v>10</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I7" s="47">
+        <v>45.78848</v>
+      </c>
+      <c r="J7" s="48">
+        <v>-4.2821305116011017E-2</v>
+      </c>
+      <c r="K7" s="47">
+        <f>M7*Q7</f>
+        <v>33.932719004800006</v>
+      </c>
+      <c r="L7" s="54">
+        <v>45.78848</v>
+      </c>
+      <c r="M7" s="47">
+        <v>2.9664320000000002</v>
+      </c>
+      <c r="N7" s="48">
+        <v>6.4785553047404063E-2</v>
+      </c>
+      <c r="O7" s="47">
+        <v>2.9664320000000002</v>
+      </c>
+      <c r="P7" s="49">
+        <v>0.74109999999999998</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11.4389</v>
+      </c>
+      <c r="R7" s="49">
+        <v>18.0383</v>
+      </c>
+      <c r="S7" s="48">
+        <v>0.1856311014966876</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U7" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V7" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W7" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="45"/>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="45">
+        <v>40865279</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>413</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>414</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="G8" s="47">
+        <v>2106</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I8" s="47">
+        <v>2110.4193416799999</v>
+      </c>
+      <c r="J8" s="48">
+        <v>-7.0838112732481195E-2</v>
+      </c>
+      <c r="K8" s="47">
+        <f>M8*Q8</f>
+        <v>1105.16712260448</v>
+      </c>
+      <c r="L8" s="54">
+        <v>2110.4193416799999</v>
+      </c>
+      <c r="M8" s="47">
+        <v>103.2885776</v>
+      </c>
+      <c r="N8" s="48">
+        <v>4.8942205731386593E-2</v>
+      </c>
+      <c r="O8" s="47">
+        <v>103.2885776</v>
+      </c>
+      <c r="P8" s="49">
+        <v>0.52370000000000005</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>10.6998</v>
+      </c>
+      <c r="R8" s="49">
+        <v>40.071100000000001</v>
+      </c>
+      <c r="S8" s="48">
+        <v>-2.753429408453156E-2</v>
+      </c>
+      <c r="T8" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U8" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V8" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W8" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X8" s="45"/>
+      <c r="Y8" s="45"/>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="45">
+        <v>8675714</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>417</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="G9" s="47">
+        <v>4508</v>
+      </c>
+      <c r="H9" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I9" s="47">
+        <v>1032.4892239999999</v>
+      </c>
+      <c r="J9" s="48">
+        <v>-0.10774161990083329</v>
+      </c>
+      <c r="K9" s="47">
+        <f>M9*Q9</f>
+        <v>173.50366092799999</v>
+      </c>
+      <c r="L9" s="54">
+        <v>1032.4892239999999</v>
+      </c>
+      <c r="M9" s="47">
+        <v>10.574719999999999</v>
+      </c>
+      <c r="N9" s="48">
+        <v>1.0241966457559849E-2</v>
+      </c>
+      <c r="O9" s="47">
+        <v>10.574719999999999</v>
+      </c>
+      <c r="P9" s="49">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="Q9" s="49">
+        <v>16.407399999999999</v>
+      </c>
+      <c r="R9" s="49">
+        <v>-9.0524000000000004</v>
+      </c>
+      <c r="S9" s="48">
+        <v>-0.119774087666231</v>
+      </c>
+      <c r="T9" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U9" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V9" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W9" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="45">
+        <v>8454443</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>419</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>420</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>421</v>
+      </c>
+      <c r="G10" s="47">
+        <v>31439</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I10" s="47">
+        <v>8733.3968800000002</v>
+      </c>
+      <c r="J10" s="48">
+        <v>9.1484422862286863E-4</v>
+      </c>
+      <c r="K10" s="47">
+        <f>M10*Q10</f>
+        <v>1689.7135179807997</v>
+      </c>
+      <c r="L10" s="54">
+        <v>8733.3968800000002</v>
+      </c>
+      <c r="M10" s="47">
+        <v>103.36788799999999</v>
+      </c>
+      <c r="N10" s="48">
+        <v>1.183593158771E-2</v>
+      </c>
+      <c r="O10" s="47">
+        <v>103.36788799999999</v>
+      </c>
+      <c r="P10" s="49">
+        <v>0.19350000000000001</v>
+      </c>
+      <c r="Q10" s="49">
+        <v>16.346599999999999</v>
+      </c>
+      <c r="R10" s="49">
+        <v>81.942800000000005</v>
+      </c>
+      <c r="S10" s="48">
+        <v>7.3027151406000801E-2</v>
+      </c>
+      <c r="T10" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U10" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V10" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W10" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X10" s="45"/>
+      <c r="Y10" s="45"/>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="45">
+        <v>5161314</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>423</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>424</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>425</v>
+      </c>
+      <c r="G11" s="47">
+        <v>368</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I11" s="47">
+        <v>29.250879999999999</v>
+      </c>
+      <c r="J11" s="48">
+        <v>-0.2086950228397102</v>
+      </c>
+      <c r="K11" s="47">
+        <f>M11*Q11</f>
+        <v>8.1513644351999996</v>
+      </c>
+      <c r="L11" s="54">
+        <v>29.250879999999999</v>
+      </c>
+      <c r="M11" s="47">
+        <v>0.434112</v>
+      </c>
+      <c r="N11" s="48">
+        <v>1.484098939929329E-2</v>
+      </c>
+      <c r="O11" s="47">
+        <v>0.434112</v>
+      </c>
+      <c r="P11" s="49">
+        <v>0.2787</v>
+      </c>
+      <c r="Q11" s="49">
+        <v>18.777100000000001</v>
+      </c>
+      <c r="R11" s="49">
+        <v>-182.5547</v>
+      </c>
+      <c r="S11" s="48">
+        <v>0.76437544621114939</v>
+      </c>
+      <c r="T11" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U11" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V11" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W11" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="45">
+        <v>8895426</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="G12" s="47">
+        <v>20</v>
+      </c>
+      <c r="H12" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I12" s="47">
+        <v>146.068352</v>
+      </c>
+      <c r="J12" s="48">
+        <v>-0.1217302976793468</v>
+      </c>
+      <c r="K12" s="47">
+        <f>M12*Q12</f>
+        <v>29.121721343999997</v>
+      </c>
+      <c r="L12" s="54">
+        <v>146.068352</v>
+      </c>
+      <c r="M12" s="47">
+        <v>2.7907199999999999</v>
+      </c>
+      <c r="N12" s="48">
+        <v>1.910557599773563E-2</v>
+      </c>
+      <c r="O12" s="47">
+        <v>2.7907199999999999</v>
+      </c>
+      <c r="P12" s="49">
+        <v>0.19939999999999999</v>
+      </c>
+      <c r="Q12" s="49">
+        <v>10.4352</v>
+      </c>
+      <c r="R12" s="49">
+        <v>-50.312600000000003</v>
+      </c>
+      <c r="S12" s="48">
+        <v>0.25992104989487319</v>
+      </c>
+      <c r="T12" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U12" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V12" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W12" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="45">
+        <v>3595177</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>429</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>430</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>431</v>
+      </c>
+      <c r="G13" s="47">
+        <v>548</v>
+      </c>
+      <c r="H13" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I13" s="47">
+        <f>MIN(I4:I10)</f>
+        <v>45.78848</v>
+      </c>
+      <c r="J13" s="48">
+        <f>MIN(J4:J10)</f>
+        <v>-0.18637283467358781</v>
+      </c>
+      <c r="K13" s="47">
+        <f>M13*Q13</f>
+        <v>184.70652086515202</v>
+      </c>
+      <c r="L13" s="54">
+        <v>1420.21983712</v>
+      </c>
+      <c r="M13" s="47">
+        <v>19.307234560000001</v>
+      </c>
+      <c r="N13" s="48">
+        <v>1.3594539419441059E-2</v>
+      </c>
+      <c r="O13" s="47">
+        <v>19.307234560000001</v>
+      </c>
+      <c r="P13" s="49">
+        <v>0.13009999999999999</v>
+      </c>
+      <c r="Q13" s="49">
+        <v>9.5667000000000009</v>
+      </c>
+      <c r="R13" s="49">
+        <v>14.537599999999999</v>
+      </c>
+      <c r="S13" s="48">
+        <v>-3.2978838112823761E-2</v>
+      </c>
+      <c r="T13" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U13" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V13" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W13" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="45"/>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="45">
+        <v>10889877</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>432</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>422</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>434</v>
+      </c>
+      <c r="G14" s="47">
+        <v>60315</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I14" s="47">
+        <f>MEDIAN(I4:I10)</f>
+        <v>414.85669200000001</v>
+      </c>
+      <c r="J14" s="48">
+        <f>MEDIAN(J4:J10)</f>
+        <v>-7.0838112732481195E-2</v>
+      </c>
+      <c r="K14" s="47">
+        <f>M14*Q14</f>
+        <v>8194.7277891049998</v>
+      </c>
+      <c r="L14" s="54">
+        <v>26330.164690000001</v>
+      </c>
+      <c r="M14" s="47">
+        <v>964.11964999999998</v>
+      </c>
+      <c r="N14" s="48">
+        <v>3.6616544611517962E-2</v>
+      </c>
+      <c r="O14" s="47">
+        <v>964.11964999999998</v>
+      </c>
+      <c r="P14" s="49">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="Q14" s="49">
+        <v>8.4997000000000007</v>
+      </c>
+      <c r="R14" s="49">
+        <v>13.6027</v>
+      </c>
+      <c r="S14" s="48">
+        <v>-8.2138005248107993E-3</v>
+      </c>
+      <c r="T14" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U14" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V14" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W14" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X14" s="45"/>
+      <c r="Y14" s="45"/>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="45">
+        <v>2446778</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>437</v>
+      </c>
+      <c r="G15" s="47">
+        <v>205090</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I15" s="47">
+        <f>MAX(I4:I10)</f>
+        <v>8733.3968800000002</v>
+      </c>
+      <c r="J15" s="48">
+        <f>MAX(J4:J10)</f>
+        <v>9.1484422862286863E-4</v>
+      </c>
+      <c r="K15" s="47">
+        <f>M15*Q15</f>
+        <v>7939.9416627230976</v>
+      </c>
+      <c r="L15" s="54">
+        <v>26507.9111932081</v>
+      </c>
+      <c r="M15" s="47">
+        <v>931.37145603789997</v>
+      </c>
+      <c r="N15" s="48">
+        <v>3.513560345247186E-2</v>
+      </c>
+      <c r="O15" s="47">
+        <v>931.37145603789997</v>
+      </c>
+      <c r="P15" s="49">
+        <v>0.29949999999999999</v>
+      </c>
+      <c r="Q15" s="49">
+        <v>8.5250000000000004</v>
+      </c>
+      <c r="R15" s="49">
+        <v>11.5809</v>
+      </c>
+      <c r="S15" s="48">
+        <v>0.43279916820204889</v>
+      </c>
+      <c r="T15" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U15" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V15" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W15" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X15" s="45"/>
+      <c r="Y15" s="45"/>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="45">
+        <v>6824987</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>449</v>
+      </c>
+      <c r="G16" s="47">
+        <v>26</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I16" s="47">
+        <v>30.39676584</v>
+      </c>
+      <c r="J16" s="48">
+        <v>-9.4670473086371221E-3</v>
+      </c>
+      <c r="K16" s="47">
+        <f>I16*P16</f>
+        <v>28.420976060400001</v>
+      </c>
+      <c r="L16" s="54">
+        <v>30.39676584</v>
+      </c>
+      <c r="M16" s="47">
+        <v>2.3246675844000002</v>
+      </c>
+      <c r="N16" s="48">
+        <v>7.6477464630164749E-2</v>
+      </c>
+      <c r="O16" s="47">
+        <v>2.3246675844000002</v>
+      </c>
+      <c r="P16" s="49">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="Q16" s="49">
+        <v>12.2258</v>
+      </c>
+      <c r="R16" s="49">
+        <v>13.133800000000001</v>
+      </c>
+      <c r="S16" s="48">
+        <v>-4.6580498005590061E-2</v>
+      </c>
+      <c r="T16" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U16" s="45">
+        <v>2025</v>
+      </c>
+      <c r="V16" s="45">
+        <v>2025</v>
+      </c>
+      <c r="W16" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="X16" s="45"/>
+      <c r="Y16" s="45"/>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="45">
+        <v>90449</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>451</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>452</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>453</v>
+      </c>
+      <c r="G17" s="45">
+        <v>21042</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I17" s="45">
+        <v>2761.0859999999998</v>
+      </c>
+      <c r="J17" s="48">
+        <v>1.4618252305513391E-2</v>
+      </c>
+      <c r="K17" s="45">
+        <v>2025</v>
+      </c>
+      <c r="L17" s="45">
+        <v>2761.0859999999998</v>
+      </c>
+      <c r="M17" s="45">
+        <v>445.56200000000001</v>
+      </c>
+      <c r="N17" s="48">
+        <v>0.16137201086818739</v>
+      </c>
+      <c r="O17" s="45">
+        <v>445.56200000000001</v>
+      </c>
+      <c r="P17" s="45">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="Q17" s="45">
+        <v>6.1849999999999996</v>
+      </c>
+      <c r="R17" s="56"/>
+      <c r="S17" s="57"/>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="45">
+        <v>1304653</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>455</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>452</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>456</v>
+      </c>
+      <c r="G18" s="45">
+        <v>19346</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I18" s="45">
+        <v>8247.18</v>
+      </c>
+      <c r="J18" s="48">
+        <v>-7.5321999400305928E-2</v>
+      </c>
+      <c r="K18" s="45">
+        <v>2025</v>
+      </c>
+      <c r="L18" s="45">
+        <v>8247.18</v>
+      </c>
+      <c r="M18" s="45">
+        <v>416.98500000000001</v>
+      </c>
+      <c r="N18" s="48">
+        <v>5.056091900504172E-2</v>
+      </c>
+      <c r="O18" s="45">
+        <v>416.98500000000001</v>
+      </c>
+      <c r="P18" s="45">
+        <v>0.46010000000000001</v>
+      </c>
+      <c r="Q18" s="45">
+        <v>9.0990000000000002</v>
+      </c>
+      <c r="R18" s="56"/>
+      <c r="S18" s="57"/>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="F19" s="58"/>
+      <c r="G19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="59"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="56"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="57"/>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="I20" s="61"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="51">
+        <f>MIN(P3:P18)</f>
+        <v>0.13009999999999999</v>
+      </c>
+      <c r="Q21" s="51">
+        <f t="shared" ref="Q21" si="0">MIN(Q3:Q18)</f>
+        <v>6.1849999999999996</v>
+      </c>
+      <c r="R21" s="51">
+        <f>MIN(R3:R16)</f>
+        <v>-182.5547</v>
+      </c>
+      <c r="S21" s="50"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="50"/>
+      <c r="V21" s="50"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="50"/>
+      <c r="Y21" s="50"/>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="51">
+        <f>MEDIAN(P3:P18)</f>
+        <v>0.46279999999999999</v>
+      </c>
+      <c r="Q22" s="51">
+        <f t="shared" ref="Q22" si="1">MEDIAN(Q3:Q18)</f>
+        <v>9.3328500000000005</v>
+      </c>
+      <c r="R22" s="51">
+        <f>MEDIAN(R3:R16)</f>
+        <v>13.36825</v>
+      </c>
+      <c r="S22" s="50"/>
+      <c r="T22" s="50"/>
+      <c r="U22" s="50"/>
+      <c r="V22" s="50"/>
+      <c r="W22" s="50"/>
+      <c r="X22" s="50"/>
+      <c r="Y22" s="50"/>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="63"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="51">
+        <f>MAX(P3:P18)</f>
+        <v>3.9767999999999999</v>
+      </c>
+      <c r="Q23" s="51">
+        <f t="shared" ref="Q23" si="2">MAX(Q3:Q18)</f>
+        <v>18.777100000000001</v>
+      </c>
+      <c r="R23" s="51">
+        <f>MAX(R3:R16)</f>
+        <v>175.791</v>
+      </c>
+      <c r="S23" s="50"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="50"/>
+      <c r="Y23" s="50"/>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="51">
+        <f>AVERAGE(P3:P18)</f>
+        <v>0.71592500000000014</v>
+      </c>
+      <c r="Q24" s="51">
+        <f t="shared" ref="Q24" si="3">AVERAGE(Q3:Q18)</f>
+        <v>10.623781249999999</v>
+      </c>
+      <c r="R24" s="51">
+        <f>AVERAGE(R3:R16)</f>
+        <v>12.679721428571431</v>
+      </c>
+      <c r="S24" s="50"/>
+      <c r="T24" s="50"/>
+      <c r="U24" s="50"/>
+      <c r="V24" s="50"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="50"/>
+      <c r="Y24" s="50"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="50" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="F27" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="H27" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="I27" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="K27" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="M27" s="44" t="s">
+        <v>377</v>
+      </c>
+      <c r="N27" s="44" t="s">
+        <v>378</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="P27" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q27" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="R27" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="S27" s="44" t="s">
+        <v>383</v>
+      </c>
+      <c r="T27" s="44" t="s">
+        <v>458</v>
+      </c>
+      <c r="U27" s="44" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="45">
+        <v>7215898</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>441</v>
+      </c>
+      <c r="G28" s="47">
+        <v>4773</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I28" s="47">
+        <v>3698.1119640000002</v>
+      </c>
+      <c r="J28" s="48">
+        <v>3.5869535869312852E-2</v>
+      </c>
+      <c r="K28" s="45"/>
+      <c r="L28" s="54">
+        <v>3698.1119640000002</v>
+      </c>
+      <c r="M28" s="47">
+        <v>153.33952217999999</v>
+      </c>
+      <c r="N28" s="48">
+        <v>4.1464272491669757E-2</v>
+      </c>
+      <c r="O28" s="47">
+        <v>153.33952217999999</v>
+      </c>
+      <c r="P28" s="47">
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="Q28" s="47">
+        <v>3.1141000000000001</v>
+      </c>
+      <c r="R28" s="47">
+        <v>4.3015999999999996</v>
+      </c>
+      <c r="S28" s="48">
+        <v>-1.8628702024887089E-2</v>
+      </c>
+      <c r="T28" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U28" s="45">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="45">
+        <v>1477589</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>442</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>443</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="G29" s="47">
+        <v>2396</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I29" s="47">
+        <v>1462.880328</v>
+      </c>
+      <c r="J29" s="48">
+        <v>5.5740146391249253E-2</v>
+      </c>
+      <c r="K29" s="45"/>
+      <c r="L29" s="54">
+        <v>1462.880328</v>
+      </c>
+      <c r="M29" s="47">
+        <v>21.017256</v>
+      </c>
+      <c r="N29" s="48">
+        <v>1.4367037137435619E-2</v>
+      </c>
+      <c r="O29" s="47">
+        <v>21.017256</v>
+      </c>
+      <c r="P29" s="47">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="Q29" s="47">
+        <v>3.6013000000000002</v>
+      </c>
+      <c r="R29" s="47">
+        <v>4.4046000000000003</v>
+      </c>
+      <c r="S29" s="48">
+        <v>0.1166112037754887</v>
+      </c>
+      <c r="T29" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U29" s="45">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="45">
+        <v>1335665</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="45" t="s">
+        <v>445</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F30" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="G30" s="47">
+        <v>130</v>
+      </c>
+      <c r="H30" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I30" s="47">
+        <v>315.91976</v>
+      </c>
+      <c r="J30" s="48">
+        <v>-2.9297465111741361E-2</v>
+      </c>
+      <c r="K30" s="45"/>
+      <c r="L30" s="54">
+        <v>315.91976</v>
+      </c>
+      <c r="M30" s="47">
+        <v>15.994263999999999</v>
+      </c>
+      <c r="N30" s="48">
+        <v>5.0627615062761512E-2</v>
+      </c>
+      <c r="O30" s="47">
+        <v>15.994263999999999</v>
+      </c>
+      <c r="P30" s="47">
+        <v>0.15160000000000001</v>
+      </c>
+      <c r="Q30" s="47">
+        <v>2.9933999999999998</v>
+      </c>
+      <c r="R30" s="47">
+        <v>7.8739999999999997</v>
+      </c>
+      <c r="S30" s="48">
+        <v>4.4751091772477818E-2</v>
+      </c>
+      <c r="T30" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="U30" s="45">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="47"/>
+      <c r="Q31" s="47"/>
+      <c r="R31" s="47"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="45"/>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="45">
+        <v>5280657</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>460</v>
+      </c>
+      <c r="D32" s="45" t="s">
+        <v>461</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>399</v>
+      </c>
+      <c r="F32" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="G32" s="45">
+        <v>864</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I32" s="45">
+        <v>215.89038575999999</v>
+      </c>
+      <c r="J32" s="48">
+        <v>0.18437568814136321</v>
+      </c>
+      <c r="K32" s="64">
+        <f>I32*P32</f>
+        <v>1997.612150398704</v>
+      </c>
+      <c r="L32" s="47">
+        <v>215.89038575999999</v>
+      </c>
+      <c r="M32" s="45">
+        <v>83.139095760000004</v>
+      </c>
+      <c r="N32" s="48">
+        <v>0.38509864840587982</v>
+      </c>
+      <c r="O32" s="45">
+        <v>83.139095760000004</v>
+      </c>
+      <c r="P32" s="45">
+        <v>9.2529000000000003</v>
+      </c>
+      <c r="Q32" s="45">
+        <v>24.0274</v>
+      </c>
+      <c r="R32" s="45">
+        <v>25.7044</v>
+      </c>
+      <c r="S32" s="48">
+        <v>5.5858922311308179E-2</v>
+      </c>
+      <c r="T32" s="45">
+        <v>17.678599999999999</v>
+      </c>
+      <c r="U32" s="45">
+        <v>9.5732999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="45">
+        <v>6824987</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>447</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="F33" s="46" t="s">
+        <v>449</v>
+      </c>
+      <c r="G33" s="45">
+        <v>26</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I33" s="45">
+        <v>30.39676584</v>
+      </c>
+      <c r="J33" s="48">
+        <v>-9.4670473086371221E-3</v>
+      </c>
+      <c r="K33" s="64">
+        <f>I33*P33</f>
+        <v>28.420976060400001</v>
+      </c>
+      <c r="L33" s="47">
+        <v>30.39676584</v>
+      </c>
+      <c r="M33" s="45">
+        <v>2.3246675844000002</v>
+      </c>
+      <c r="N33" s="48">
+        <v>7.6477464630164749E-2</v>
+      </c>
+      <c r="O33" s="45">
+        <v>2.3246675844000002</v>
+      </c>
+      <c r="P33" s="45">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="Q33" s="45">
+        <v>12.2258</v>
+      </c>
+      <c r="R33" s="45">
+        <v>13.133800000000001</v>
+      </c>
+      <c r="S33" s="48">
+        <v>-4.6580498005590061E-2</v>
+      </c>
+      <c r="T33" s="45">
+        <v>1.1982999999999999</v>
+      </c>
+      <c r="U33" s="45">
+        <v>0.79769999999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="45">
+        <v>40994430</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="45" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="48" t="s">
-        <v>367</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>368</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>369</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>304</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>370</v>
-      </c>
-      <c r="G3" s="48" t="s">
-        <v>371</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>372</v>
-      </c>
-      <c r="I3" s="48" t="s">
-        <v>373</v>
-      </c>
-      <c r="J3" s="48" t="s">
-        <v>374</v>
-      </c>
-      <c r="K3" s="48" t="s">
-        <v>375</v>
-      </c>
-      <c r="L3" s="48" t="s">
-        <v>376</v>
-      </c>
-      <c r="M3" s="48" t="s">
-        <v>377</v>
-      </c>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q3" s="48" t="s">
-        <v>379</v>
-      </c>
-      <c r="R3" s="48" t="s">
-        <v>380</v>
-      </c>
-      <c r="S3" s="48" t="s">
-        <v>381</v>
-      </c>
-      <c r="T3" s="48" t="s">
-        <v>382</v>
-      </c>
-      <c r="U3" s="48" t="s">
-        <v>383</v>
-      </c>
-      <c r="V3" s="48" t="s">
-        <v>384</v>
-      </c>
-      <c r="W3" s="48" t="s">
-        <v>385</v>
-      </c>
-      <c r="X3" s="48" t="s">
-        <v>386</v>
-      </c>
-      <c r="Y3" s="48" t="s">
-        <v>387</v>
-      </c>
-      <c r="Z3" s="48" t="s">
-        <v>388</v>
-      </c>
-      <c r="AA3" s="48" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="49">
-        <v>11028540</v>
-      </c>
-      <c r="C4" s="49" t="s">
-        <v>390</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>391</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>392</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>393</v>
-      </c>
-      <c r="G4" s="51">
-        <v>590</v>
-      </c>
-      <c r="H4" s="49" t="s">
+      <c r="E34" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F34" s="46" t="s">
+        <v>464</v>
+      </c>
+      <c r="G34" s="45">
+        <v>63</v>
+      </c>
+      <c r="H34" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="I4" s="51">
-        <v>216.1122048</v>
-      </c>
-      <c r="J4" s="52">
-        <v>0.1005670513875327</v>
-      </c>
-      <c r="K4" s="51">
-        <f>M4*S4</f>
-        <v>859.42735012224</v>
-      </c>
-      <c r="L4" s="51">
-        <v>216.1122048</v>
-      </c>
-      <c r="M4" s="51">
-        <v>97.524777599999993</v>
-      </c>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="52">
-        <v>0.45126918070293082</v>
-      </c>
-      <c r="Q4" s="51">
-        <v>97.524777599999993</v>
-      </c>
-      <c r="R4" s="53">
-        <v>3.9767999999999999</v>
-      </c>
-      <c r="S4" s="53">
-        <v>8.8124000000000002</v>
-      </c>
-      <c r="T4" s="53">
-        <v>9.9036000000000008</v>
-      </c>
-      <c r="U4" s="52">
-        <v>2.1822889132818268E-2</v>
-      </c>
-      <c r="V4" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W4" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X4" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y4" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z4" s="49"/>
-      <c r="AA4" s="49"/>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="49">
-        <v>5280480</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>397</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>398</v>
-      </c>
-      <c r="E5" s="49" t="s">
+      <c r="I34" s="45">
+        <v>41.907454919999999</v>
+      </c>
+      <c r="J34" s="48">
+        <v>1.509288015155964</v>
+      </c>
+      <c r="K34" s="64">
+        <f>I34*P34</f>
+        <v>11.470070411604</v>
+      </c>
+      <c r="L34" s="47">
+        <v>41.907454919999999</v>
+      </c>
+      <c r="M34" s="45">
+        <v>2.6496237300000001</v>
+      </c>
+      <c r="N34" s="48">
+        <v>6.3225593991762266E-2</v>
+      </c>
+      <c r="O34" s="45">
+        <v>2.6496237300000001</v>
+      </c>
+      <c r="P34" s="45">
+        <v>0.2737</v>
+      </c>
+      <c r="Q34" s="45">
+        <v>4.3282999999999996</v>
+      </c>
+      <c r="R34" s="45">
+        <v>1.3696999999999999</v>
+      </c>
+      <c r="S34" s="48">
+        <v>0.17334388455582039</v>
+      </c>
+      <c r="T34" s="45">
+        <v>3.5112000000000001</v>
+      </c>
+      <c r="U34" s="45">
+        <v>1.671</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="45">
+        <v>5159695</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F35" s="46" t="s">
+        <v>467</v>
+      </c>
+      <c r="G35" s="45">
+        <v>274</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I35" s="45">
+        <v>149.82985199999999</v>
+      </c>
+      <c r="J35" s="48">
+        <v>-6.2927868441163715E-2</v>
+      </c>
+      <c r="K35" s="64">
+        <f>I35*P35</f>
+        <v>38.745999727199994</v>
+      </c>
+      <c r="L35" s="47">
+        <v>149.82985199999999</v>
+      </c>
+      <c r="M35" s="45">
+        <v>6.6016589999999997</v>
+      </c>
+      <c r="N35" s="48">
+        <v>4.4061039318119333E-2</v>
+      </c>
+      <c r="O35" s="45">
+        <v>6.6016589999999997</v>
+      </c>
+      <c r="P35" s="45">
+        <v>0.2586</v>
+      </c>
+      <c r="Q35" s="45">
+        <v>5.8697999999999997</v>
+      </c>
+      <c r="R35" s="45">
+        <v>8.7910000000000004</v>
+      </c>
+      <c r="S35" s="48">
+        <v>-1.533260983111173E-2</v>
+      </c>
+      <c r="T35" s="45">
+        <v>0.43809999999999999</v>
+      </c>
+      <c r="U35" s="45">
+        <v>0.64470000000000005</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="45">
+        <v>301296</v>
+      </c>
+      <c r="C36" s="45" t="s">
+        <v>468</v>
+      </c>
+      <c r="D36" s="45" t="s">
+        <v>469</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="F36" s="46" t="s">
+        <v>470</v>
+      </c>
+      <c r="G36" s="45">
+        <v>86</v>
+      </c>
+      <c r="H36" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I36" s="45">
+        <v>20.014736490000001</v>
+      </c>
+      <c r="J36" s="48">
+        <v>0.20298911147211071</v>
+      </c>
+      <c r="K36" s="64">
+        <f>I36*P36</f>
+        <v>3.854838247974</v>
+      </c>
+      <c r="L36" s="47">
+        <v>20.014736490000001</v>
+      </c>
+      <c r="M36" s="45">
+        <v>1.4144223</v>
+      </c>
+      <c r="N36" s="48">
+        <v>7.0669044316755844E-2</v>
+      </c>
+      <c r="O36" s="45">
+        <v>1.4144223</v>
+      </c>
+      <c r="P36" s="45">
+        <v>0.19259999999999999</v>
+      </c>
+      <c r="Q36" s="45">
+        <v>2.7252000000000001</v>
+      </c>
+      <c r="R36" s="45">
+        <v>4.5</v>
+      </c>
+      <c r="S36" s="48">
+        <v>9.2240238124367213E-2</v>
+      </c>
+      <c r="T36" s="45">
+        <v>0.75009999999999999</v>
+      </c>
+      <c r="U36" s="45">
+        <v>0.42449999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="45">
+        <v>6824108</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>471</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>472</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="F37" s="46" t="s">
+        <v>473</v>
+      </c>
+      <c r="G37" s="45">
+        <v>5164</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I37" s="45">
+        <v>3846.5078400000002</v>
+      </c>
+      <c r="J37" s="48">
+        <v>0.13007224057053149</v>
+      </c>
+      <c r="K37" s="64">
+        <f>I37*P37</f>
+        <v>712.75790275200006</v>
+      </c>
+      <c r="L37" s="47">
+        <v>3846.5078400000002</v>
+      </c>
+      <c r="M37" s="45">
+        <v>167.27974368</v>
+      </c>
+      <c r="N37" s="48">
+        <v>4.3488730723606157E-2</v>
+      </c>
+      <c r="O37" s="45">
+        <v>167.27974368</v>
+      </c>
+      <c r="P37" s="45">
+        <v>0.18529999999999999</v>
+      </c>
+      <c r="Q37" s="45">
+        <v>4.2598000000000003</v>
+      </c>
+      <c r="R37" s="45">
+        <v>6.8963000000000001</v>
+      </c>
+      <c r="S37" s="48">
+        <v>0.1160298358915009</v>
+      </c>
+      <c r="T37" s="45">
+        <v>0.20269999999999999</v>
+      </c>
+      <c r="U37" s="45">
+        <v>0.1447</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="45">
+        <v>3602587</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>475</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>403</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="G38" s="45">
+        <v>205</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="I38" s="45">
+        <v>32.691894480000002</v>
+      </c>
+      <c r="J38" s="48">
+        <v>4.0104447124864377E-2</v>
+      </c>
+      <c r="K38" s="64">
+        <f>I38*P38</f>
+        <v>32.358437156303999</v>
+      </c>
+      <c r="L38" s="47">
+        <v>32.691894480000002</v>
+      </c>
+      <c r="M38" s="45">
+        <v>4.3039365599999986</v>
+      </c>
+      <c r="N38" s="48">
+        <v>0.13165148818870159</v>
+      </c>
+      <c r="O38" s="45">
+        <v>4.3039365599999986</v>
+      </c>
+      <c r="P38" s="45">
+        <v>0.98980000000000001</v>
+      </c>
+      <c r="Q38" s="45">
+        <v>7.5182000000000002</v>
+      </c>
+      <c r="R38" s="45">
+        <v>9.1770999999999994</v>
+      </c>
+      <c r="S38" s="48">
+        <v>0</v>
+      </c>
+      <c r="T38" s="45">
+        <v>2.4251</v>
+      </c>
+      <c r="U38" s="45">
+        <v>1.4571000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="45">
+        <v>5284152</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>478</v>
+      </c>
+      <c r="E39" s="45" t="s">
         <v>399</v>
       </c>
-      <c r="F5" s="50" t="s">
-        <v>400</v>
-      </c>
-      <c r="G5" s="51">
-        <v>1135</v>
-      </c>
-      <c r="H5" s="49" t="s">
+      <c r="F39" s="46" t="s">
+        <v>479</v>
+      </c>
+      <c r="G39" s="45">
+        <v>81</v>
+      </c>
+      <c r="H39" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="I5" s="51">
-        <v>414.85669200000001</v>
-      </c>
-      <c r="J5" s="52">
-        <v>-3.6945463803843233E-2</v>
-      </c>
-      <c r="K5" s="51">
-        <f>M5*S5</f>
-        <v>429.38360761274998</v>
-      </c>
-      <c r="L5" s="51">
-        <v>414.85669200000001</v>
-      </c>
-      <c r="M5" s="51">
-        <v>49.033185750000001</v>
-      </c>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="52">
-        <v>0.1181930693069307</v>
-      </c>
-      <c r="Q5" s="51">
-        <v>49.033185750000001</v>
-      </c>
-      <c r="R5" s="53">
-        <v>1.0349999999999999</v>
-      </c>
-      <c r="S5" s="53">
-        <v>8.7569999999999997</v>
-      </c>
-      <c r="T5" s="53">
-        <v>30.8672</v>
-      </c>
-      <c r="U5" s="52">
-        <v>3.3556562757084192E-2</v>
-      </c>
-      <c r="V5" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W5" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X5" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y5" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z5" s="49"/>
-      <c r="AA5" s="49"/>
-    </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="49">
-        <v>18285512</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>401</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="49" t="s">
+      <c r="I39" s="45">
+        <v>57.249314640000001</v>
+      </c>
+      <c r="J39" s="48">
+        <v>-0.20056374913631431</v>
+      </c>
+      <c r="K39" s="64">
+        <f>I39*P39</f>
+        <v>43.263307073448004</v>
+      </c>
+      <c r="L39" s="47">
+        <v>57.249314640000001</v>
+      </c>
+      <c r="M39" s="45">
+        <v>3.8191305600000001</v>
+      </c>
+      <c r="N39" s="48">
+        <v>6.6710502719827841E-2</v>
+      </c>
+      <c r="O39" s="45">
+        <v>3.8191305600000001</v>
+      </c>
+      <c r="P39" s="45">
+        <v>0.75570000000000004</v>
+      </c>
+      <c r="Q39" s="45">
+        <v>11.328200000000001</v>
+      </c>
+      <c r="R39" s="45">
+        <v>33.742699999999999</v>
+      </c>
+      <c r="S39" s="48">
+        <v>-1.204936598747575E-2</v>
+      </c>
+      <c r="T39" s="45">
+        <v>0.92910000000000004</v>
+      </c>
+      <c r="U39" s="45">
+        <v>0.23300000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="45">
+        <v>5139529</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>480</v>
+      </c>
+      <c r="D40" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="E40" s="45" t="s">
         <v>403</v>
       </c>
-      <c r="F6" s="50" t="s">
-        <v>404</v>
-      </c>
-      <c r="G6" s="51">
-        <v>666</v>
-      </c>
-      <c r="H6" s="49" t="s">
+      <c r="F40" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="G40" s="45">
+        <v>858</v>
+      </c>
+      <c r="H40" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="I6" s="51">
-        <v>158.97705495</v>
-      </c>
-      <c r="J6" s="52">
-        <v>-0.1743952190243411</v>
-      </c>
-      <c r="K6" s="51">
-        <f>M6*S6</f>
-        <v>74.010890240799995</v>
-      </c>
-      <c r="L6" s="51">
-        <v>158.97705495</v>
-      </c>
-      <c r="M6" s="51">
-        <v>10.53685795</v>
-      </c>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="52">
-        <v>6.6279111493881659E-2</v>
-      </c>
-      <c r="Q6" s="51">
-        <v>10.53685795</v>
-      </c>
-      <c r="R6" s="53">
-        <v>0.46550000000000002</v>
-      </c>
-      <c r="S6" s="53">
-        <v>7.024</v>
-      </c>
-      <c r="T6" s="53">
-        <v>175.791</v>
-      </c>
-      <c r="U6" s="52">
-        <v>0.15610954377561809</v>
-      </c>
-      <c r="V6" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W6" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X6" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y6" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="49"/>
-    </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="49">
-        <v>501430</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>405</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>406</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F7" s="50" t="s">
-        <v>408</v>
-      </c>
-      <c r="G7" s="51">
-        <v>4145</v>
-      </c>
-      <c r="H7" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I7" s="51">
-        <v>234.92665768000001</v>
-      </c>
-      <c r="J7" s="52">
-        <v>-0.18637283467358781</v>
-      </c>
-      <c r="K7" s="51">
-        <f>M7*S7</f>
-        <v>173.627679657952</v>
-      </c>
-      <c r="L7" s="51">
-        <v>234.92665768000001</v>
-      </c>
-      <c r="M7" s="51">
-        <v>24.179097280000001</v>
-      </c>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="52">
-        <v>0.1029218970668497</v>
-      </c>
-      <c r="Q7" s="51">
-        <v>24.179097280000001</v>
-      </c>
-      <c r="R7" s="53">
-        <v>0.73909999999999998</v>
-      </c>
-      <c r="S7" s="53">
-        <v>7.1809000000000003</v>
-      </c>
-      <c r="T7" s="53">
-        <v>9.9667999999999992</v>
-      </c>
-      <c r="U7" s="52">
-        <v>-0.14732004381615971</v>
-      </c>
-      <c r="V7" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W7" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X7" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y7" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-    </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="49">
-        <v>5174553</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>409</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>410</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>412</v>
-      </c>
-      <c r="G8" s="51">
-        <v>10</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I8" s="51">
-        <v>45.78848</v>
-      </c>
-      <c r="J8" s="52">
-        <v>-4.2821305116011017E-2</v>
-      </c>
-      <c r="K8" s="51">
-        <f>M8*S8</f>
-        <v>33.932719004800006</v>
-      </c>
-      <c r="L8" s="51">
-        <v>45.78848</v>
-      </c>
-      <c r="M8" s="51">
-        <v>2.9664320000000002</v>
-      </c>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="52">
-        <v>6.4785553047404063E-2</v>
-      </c>
-      <c r="Q8" s="51">
-        <v>2.9664320000000002</v>
-      </c>
-      <c r="R8" s="53">
-        <v>0.74109999999999998</v>
-      </c>
-      <c r="S8" s="53">
-        <v>11.4389</v>
-      </c>
-      <c r="T8" s="53">
-        <v>18.0383</v>
-      </c>
-      <c r="U8" s="52">
-        <v>0.1856311014966876</v>
-      </c>
-      <c r="V8" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W8" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X8" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y8" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z8" s="49"/>
-      <c r="AA8" s="49"/>
-    </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="49">
-        <v>40865279</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>413</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>414</v>
-      </c>
-      <c r="E9" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>415</v>
-      </c>
-      <c r="G9" s="51">
-        <v>2106</v>
-      </c>
-      <c r="H9" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I9" s="51">
-        <v>2110.4193416799999</v>
-      </c>
-      <c r="J9" s="52">
-        <v>-7.0838112732481195E-2</v>
-      </c>
-      <c r="K9" s="51">
-        <f>M9*S9</f>
-        <v>1105.16712260448</v>
-      </c>
-      <c r="L9" s="51">
-        <v>2110.4193416799999</v>
-      </c>
-      <c r="M9" s="51">
-        <v>103.2885776</v>
-      </c>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="52">
-        <v>4.8942205731386593E-2</v>
-      </c>
-      <c r="Q9" s="51">
-        <v>103.2885776</v>
-      </c>
-      <c r="R9" s="53">
-        <v>0.52370000000000005</v>
-      </c>
-      <c r="S9" s="53">
-        <v>10.6998</v>
-      </c>
-      <c r="T9" s="53">
-        <v>40.071100000000001</v>
-      </c>
-      <c r="U9" s="52">
-        <v>-2.753429408453156E-2</v>
-      </c>
-      <c r="V9" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W9" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X9" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y9" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-    </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="49">
-        <v>8675714</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>416</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>417</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F10" s="50" t="s">
-        <v>418</v>
-      </c>
-      <c r="G10" s="51">
-        <v>4508</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I10" s="51">
-        <v>1032.4892239999999</v>
-      </c>
-      <c r="J10" s="52">
-        <v>-0.10774161990083329</v>
-      </c>
-      <c r="K10" s="51">
-        <f>M10*S10</f>
-        <v>173.50366092799999</v>
-      </c>
-      <c r="L10" s="51">
-        <v>1032.4892239999999</v>
-      </c>
-      <c r="M10" s="51">
-        <v>10.574719999999999</v>
-      </c>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="52">
-        <v>1.0241966457559849E-2</v>
-      </c>
-      <c r="Q10" s="51">
-        <v>10.574719999999999</v>
-      </c>
-      <c r="R10" s="53">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="S10" s="53">
-        <v>16.407399999999999</v>
-      </c>
-      <c r="T10" s="53">
-        <v>-9.0524000000000004</v>
-      </c>
-      <c r="U10" s="52">
-        <v>-0.119774087666231</v>
-      </c>
-      <c r="V10" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W10" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X10" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y10" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="49"/>
-    </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="49">
-        <v>8454443</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>419</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>420</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F11" s="50" t="s">
-        <v>421</v>
-      </c>
-      <c r="G11" s="51">
-        <v>31439</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I11" s="51">
-        <v>8733.3968800000002</v>
-      </c>
-      <c r="J11" s="52">
-        <v>9.1484422862286863E-4</v>
-      </c>
-      <c r="K11" s="51">
-        <f>M11*S11</f>
-        <v>1689.7135179807997</v>
-      </c>
-      <c r="L11" s="51">
-        <v>8733.3968800000002</v>
-      </c>
-      <c r="M11" s="51">
-        <v>103.36788799999999</v>
-      </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="52">
-        <v>1.183593158771E-2</v>
-      </c>
-      <c r="Q11" s="51">
-        <v>103.36788799999999</v>
-      </c>
-      <c r="R11" s="53">
-        <v>0.19350000000000001</v>
-      </c>
-      <c r="S11" s="53">
-        <v>16.346599999999999</v>
-      </c>
-      <c r="T11" s="53">
-        <v>81.942800000000005</v>
-      </c>
-      <c r="U11" s="52">
-        <v>7.3027151406000801E-2</v>
-      </c>
-      <c r="V11" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W11" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X11" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y11" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="49"/>
-    </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="49">
-        <v>12444477</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>423</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>424</v>
-      </c>
-      <c r="G12" s="51">
-        <v>5307</v>
-      </c>
-      <c r="H12" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I12" s="51">
-        <v>1389.3089663200001</v>
-      </c>
-      <c r="J12" s="52">
-        <v>1.000595864584364E-2</v>
-      </c>
-      <c r="K12" s="51">
-        <f>M12*S12</f>
-        <v>460.95447274022803</v>
-      </c>
-      <c r="L12" s="51">
-        <v>1389.3089663200001</v>
-      </c>
-      <c r="M12" s="51">
-        <v>50.992231240000002</v>
-      </c>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="52">
-        <v>3.6703305367033062E-2</v>
-      </c>
-      <c r="Q12" s="51">
-        <v>50.992231240000002</v>
-      </c>
-      <c r="R12" s="53">
-        <v>0.33179999999999998</v>
-      </c>
-      <c r="S12" s="53">
-        <v>9.0396999999999998</v>
-      </c>
-      <c r="T12" s="53">
-        <v>23.470700000000001</v>
-      </c>
-      <c r="U12" s="52">
-        <v>1.381443484904632E-2</v>
-      </c>
-      <c r="V12" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W12" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X12" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y12" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-    </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="49">
-        <v>5161314</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>425</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>426</v>
-      </c>
-      <c r="E13" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="F13" s="50" t="s">
-        <v>427</v>
-      </c>
-      <c r="G13" s="51">
-        <v>368</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I13" s="51">
-        <v>29.250879999999999</v>
-      </c>
-      <c r="J13" s="52">
-        <v>-0.2086950228397102</v>
-      </c>
-      <c r="K13" s="51">
-        <f>M13*S13</f>
-        <v>8.1513644351999996</v>
-      </c>
-      <c r="L13" s="51">
-        <v>29.250879999999999</v>
-      </c>
-      <c r="M13" s="51">
-        <v>0.434112</v>
-      </c>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="52">
-        <v>1.484098939929329E-2</v>
-      </c>
-      <c r="Q13" s="51">
-        <v>0.434112</v>
-      </c>
-      <c r="R13" s="53">
-        <v>0.2787</v>
-      </c>
-      <c r="S13" s="53">
-        <v>18.777100000000001</v>
-      </c>
-      <c r="T13" s="53">
-        <v>-182.5547</v>
-      </c>
-      <c r="U13" s="52">
-        <v>0.76437544621114939</v>
-      </c>
-      <c r="V13" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W13" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X13" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y13" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-    </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="49">
-        <v>8895426</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>428</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>429</v>
-      </c>
-      <c r="E14" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="F14" s="50" t="s">
-        <v>430</v>
-      </c>
-      <c r="G14" s="51">
-        <v>20</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I14" s="51">
-        <v>146.068352</v>
-      </c>
-      <c r="J14" s="52">
-        <v>-0.1217302976793468</v>
-      </c>
-      <c r="K14" s="51">
-        <f>M14*S14</f>
-        <v>29.121721343999997</v>
-      </c>
-      <c r="L14" s="51">
-        <v>146.068352</v>
-      </c>
-      <c r="M14" s="51">
-        <v>2.7907199999999999</v>
-      </c>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="52">
-        <v>1.910557599773563E-2</v>
-      </c>
-      <c r="Q14" s="51">
-        <v>2.7907199999999999</v>
-      </c>
-      <c r="R14" s="53">
-        <v>0.19939999999999999</v>
-      </c>
-      <c r="S14" s="53">
-        <v>10.4352</v>
-      </c>
-      <c r="T14" s="53">
-        <v>-50.312600000000003</v>
-      </c>
-      <c r="U14" s="52">
-        <v>0.25992104989487319</v>
-      </c>
-      <c r="V14" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W14" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X14" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y14" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z14" s="49"/>
-      <c r="AA14" s="49"/>
-    </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="49">
-        <v>3595177</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>431</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>432</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="F15" s="50" t="s">
-        <v>433</v>
-      </c>
-      <c r="G15" s="51">
-        <v>548</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I15" s="51">
-        <v>1420.21983712</v>
-      </c>
-      <c r="J15" s="52">
-        <v>-5.0861740463697187E-2</v>
-      </c>
-      <c r="K15" s="51">
-        <f>M15*S15</f>
-        <v>184.70652086515202</v>
-      </c>
-      <c r="L15" s="51">
-        <v>1420.21983712</v>
-      </c>
-      <c r="M15" s="51">
-        <v>19.307234560000001</v>
-      </c>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="52">
-        <v>1.3594539419441059E-2</v>
-      </c>
-      <c r="Q15" s="51">
-        <v>19.307234560000001</v>
-      </c>
-      <c r="R15" s="53">
-        <v>0.13009999999999999</v>
-      </c>
-      <c r="S15" s="53">
-        <v>9.5667000000000009</v>
-      </c>
-      <c r="T15" s="53">
-        <v>14.537599999999999</v>
-      </c>
-      <c r="U15" s="52">
-        <v>-3.2978838112823761E-2</v>
-      </c>
-      <c r="V15" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W15" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X15" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y15" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z15" s="49"/>
-      <c r="AA15" s="49"/>
-    </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="49">
-        <v>10889877</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>434</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>435</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>423</v>
-      </c>
-      <c r="F16" s="50" t="s">
-        <v>436</v>
-      </c>
-      <c r="G16" s="51">
-        <v>60315</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I16" s="51">
-        <v>26330.164690000001</v>
-      </c>
-      <c r="J16" s="52">
-        <v>-5.7550626687547957E-2</v>
-      </c>
-      <c r="K16" s="51">
-        <f>M16*S16</f>
-        <v>8194.7277891049998</v>
-      </c>
-      <c r="L16" s="51">
-        <v>26330.164690000001</v>
-      </c>
-      <c r="M16" s="51">
-        <v>964.11964999999998</v>
-      </c>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="52">
-        <v>3.6616544611517962E-2</v>
-      </c>
-      <c r="Q16" s="51">
-        <v>964.11964999999998</v>
-      </c>
-      <c r="R16" s="53">
-        <v>0.31119999999999998</v>
-      </c>
-      <c r="S16" s="53">
-        <v>8.4997000000000007</v>
-      </c>
-      <c r="T16" s="53">
-        <v>13.6027</v>
-      </c>
-      <c r="U16" s="52">
-        <v>-8.2138005248107993E-3</v>
-      </c>
-      <c r="V16" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W16" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X16" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y16" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z16" s="49"/>
-      <c r="AA16" s="49"/>
-    </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="49">
-        <v>2446778</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>365</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>437</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>438</v>
-      </c>
-      <c r="F17" s="50" t="s">
-        <v>439</v>
-      </c>
-      <c r="G17" s="51">
-        <v>205090</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I17" s="51">
-        <v>26507.9111932081</v>
-      </c>
-      <c r="J17" s="52">
-        <v>-5.7751746319654176E-3</v>
-      </c>
-      <c r="K17" s="51">
-        <f>M17*S17</f>
-        <v>7939.9416627230976</v>
-      </c>
-      <c r="L17" s="51">
-        <v>26507.9111932081</v>
-      </c>
-      <c r="M17" s="51">
-        <v>931.37145603789997</v>
-      </c>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="52">
-        <v>3.513560345247186E-2</v>
-      </c>
-      <c r="Q17" s="51">
-        <v>931.37145603789997</v>
-      </c>
-      <c r="R17" s="53">
-        <v>0.29949999999999999</v>
-      </c>
-      <c r="S17" s="53">
-        <v>8.5250000000000004</v>
-      </c>
-      <c r="T17" s="53">
-        <v>11.5809</v>
-      </c>
-      <c r="U17" s="52">
-        <v>0.43279916820204889</v>
-      </c>
-      <c r="V17" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W17" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X17" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y17" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z17" s="49"/>
-      <c r="AA17" s="49"/>
-    </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="54"/>
-      <c r="R19" s="55">
-        <f>MIN(R4:R17)</f>
-        <v>0.13009999999999999</v>
-      </c>
-      <c r="S19" s="55">
-        <f>MIN(S4:S17)</f>
-        <v>7.024</v>
-      </c>
-      <c r="T19" s="55">
-        <f>MIN(T4:T17)</f>
-        <v>-182.5547</v>
-      </c>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
-      <c r="W19" s="54"/>
-      <c r="X19" s="54"/>
-      <c r="Y19" s="54"/>
-      <c r="Z19" s="54"/>
-      <c r="AA19" s="54"/>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="55">
-        <f>MEDIAN(R4:R17)</f>
-        <v>0.32150000000000001</v>
-      </c>
-      <c r="S20" s="55">
-        <f>MEDIAN(S4:S17)</f>
-        <v>9.3032000000000004</v>
-      </c>
-      <c r="T20" s="55">
-        <f>MEDIAN(T4:T17)</f>
-        <v>14.07015</v>
-      </c>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
-      <c r="W20" s="54"/>
-      <c r="X20" s="54"/>
-      <c r="Y20" s="54"/>
-      <c r="Z20" s="54"/>
-      <c r="AA20" s="54"/>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="55">
-        <f>MAX(R4:R17)</f>
-        <v>3.9767999999999999</v>
-      </c>
-      <c r="S21" s="55">
-        <f t="shared" ref="S21:T21" si="0">MAX(S4:S17)</f>
-        <v>18.777100000000001</v>
-      </c>
-      <c r="T21" s="55">
-        <f t="shared" si="0"/>
-        <v>175.791</v>
-      </c>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
-      <c r="X21" s="54"/>
-      <c r="Y21" s="54"/>
-      <c r="Z21" s="54"/>
-      <c r="AA21" s="54"/>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="55">
-        <f>AVERAGE(R4:R17)</f>
-        <v>0.67095714285714292</v>
-      </c>
-      <c r="S22" s="55">
-        <f>AVERAGE(S4:S17)</f>
-        <v>10.822171428571426</v>
-      </c>
-      <c r="T22" s="55">
-        <f>AVERAGE(T4:T17)</f>
-        <v>13.418071428571434</v>
-      </c>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
-      <c r="W22" s="54"/>
-      <c r="X22" s="54"/>
-      <c r="Y22" s="54"/>
-      <c r="Z22" s="54"/>
-      <c r="AA22" s="54"/>
-    </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="49">
-        <v>7215898</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>440</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>441</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>442</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="G25" s="51">
-        <v>4773</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I25" s="51">
-        <v>3698.1119640000002</v>
-      </c>
-      <c r="J25" s="52">
-        <v>3.5869535869312852E-2</v>
-      </c>
-      <c r="K25" s="49"/>
-      <c r="L25" s="51">
-        <v>3698.1119640000002</v>
-      </c>
-      <c r="M25" s="51">
-        <v>153.33952217999999</v>
-      </c>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="52">
-        <v>4.1464272491669757E-2</v>
-      </c>
-      <c r="Q25" s="51">
-        <v>153.33952217999999</v>
-      </c>
-      <c r="R25" s="51">
-        <v>0.12909999999999999</v>
-      </c>
-      <c r="S25" s="51">
-        <v>3.1141000000000001</v>
-      </c>
-      <c r="T25" s="51">
-        <v>4.3015999999999996</v>
-      </c>
-      <c r="U25" s="52">
-        <v>-1.8628702024887089E-2</v>
-      </c>
-      <c r="V25" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W25" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X25" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y25" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z25" s="49"/>
-      <c r="AA25" s="49"/>
-    </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="49">
-        <v>1477589</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>444</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>445</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>446</v>
-      </c>
-      <c r="G26" s="51">
-        <v>2396</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I26" s="51">
-        <v>1462.880328</v>
-      </c>
-      <c r="J26" s="52">
-        <v>5.5740146391249253E-2</v>
-      </c>
-      <c r="K26" s="49"/>
-      <c r="L26" s="51">
-        <v>1462.880328</v>
-      </c>
-      <c r="M26" s="51">
-        <v>21.017256</v>
-      </c>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="52">
-        <v>1.4367037137435619E-2</v>
-      </c>
-      <c r="Q26" s="51">
-        <v>21.017256</v>
-      </c>
-      <c r="R26" s="51">
-        <v>5.1700000000000003E-2</v>
-      </c>
-      <c r="S26" s="51">
-        <v>3.6013000000000002</v>
-      </c>
-      <c r="T26" s="51">
-        <v>4.4046000000000003</v>
-      </c>
-      <c r="U26" s="52">
-        <v>0.1166112037754887</v>
-      </c>
-      <c r="V26" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W26" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X26" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y26" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="49"/>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="49">
-        <v>1335665</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>447</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F27" s="50" t="s">
-        <v>448</v>
-      </c>
-      <c r="G27" s="51">
-        <v>130</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I27" s="51">
-        <v>315.91976</v>
-      </c>
-      <c r="J27" s="52">
-        <v>-2.9297465111741361E-2</v>
-      </c>
-      <c r="K27" s="49"/>
-      <c r="L27" s="51">
-        <v>315.91976</v>
-      </c>
-      <c r="M27" s="51">
-        <v>15.994263999999999</v>
-      </c>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="52">
-        <v>5.0627615062761512E-2</v>
-      </c>
-      <c r="Q27" s="51">
-        <v>15.994263999999999</v>
-      </c>
-      <c r="R27" s="51">
-        <v>0.15160000000000001</v>
-      </c>
-      <c r="S27" s="51">
-        <v>2.9933999999999998</v>
-      </c>
-      <c r="T27" s="51">
-        <v>7.8739999999999997</v>
-      </c>
-      <c r="U27" s="52">
-        <v>4.4751091772477818E-2</v>
-      </c>
-      <c r="V27" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W27" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X27" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y27" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z27" s="49"/>
-      <c r="AA27" s="49"/>
-    </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="49">
-        <v>3593079</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>449</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>450</v>
-      </c>
-      <c r="E28" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F28" s="50" t="s">
-        <v>451</v>
-      </c>
-      <c r="G28" s="51">
-        <v>244</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I28" s="51">
-        <v>527.28197599999999</v>
-      </c>
-      <c r="J28" s="52">
-        <v>-4.1213880706728601E-3</v>
-      </c>
-      <c r="K28" s="49"/>
-      <c r="L28" s="51">
-        <v>527.28197599999999</v>
-      </c>
-      <c r="M28" s="51">
-        <v>5.4301187199999994</v>
-      </c>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="52">
-        <v>1.029832038104788E-2</v>
-      </c>
-      <c r="Q28" s="51">
-        <v>5.4301187199999994</v>
-      </c>
-      <c r="R28" s="51">
-        <v>3.0200000000000001E-2</v>
-      </c>
-      <c r="S28" s="51">
-        <v>2.9304999999999999</v>
-      </c>
-      <c r="T28" s="51">
-        <v>4.4635999999999996</v>
-      </c>
-      <c r="U28" s="52">
-        <v>-0.34692673288716858</v>
-      </c>
-      <c r="V28" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W28" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X28" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y28" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z28" s="49"/>
-      <c r="AA28" s="49"/>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="49">
-        <v>2122004</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>452</v>
-      </c>
-      <c r="D29" s="49" t="s">
-        <v>453</v>
-      </c>
-      <c r="E29" s="49" t="s">
-        <v>442</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>454</v>
-      </c>
-      <c r="G29" s="51">
-        <v>2466</v>
-      </c>
-      <c r="H29" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I29" s="51">
-        <v>1200.9850208590001</v>
-      </c>
-      <c r="J29" s="52">
-        <v>9.5711533407700569E-2</v>
-      </c>
-      <c r="K29" s="49"/>
-      <c r="L29" s="51">
-        <v>1200.9850208590001</v>
-      </c>
-      <c r="M29" s="51">
-        <v>32.640869760000001</v>
-      </c>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="52">
-        <v>2.7178415378281529E-2</v>
-      </c>
-      <c r="Q29" s="51">
-        <v>32.640869760000001</v>
-      </c>
-      <c r="R29" s="51">
-        <v>0.13880000000000001</v>
-      </c>
-      <c r="S29" s="51">
-        <v>5.1085000000000003</v>
-      </c>
-      <c r="T29" s="51">
-        <v>6.3617999999999997</v>
-      </c>
-      <c r="U29" s="52">
-        <v>0.11208400462918219</v>
-      </c>
-      <c r="V29" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W29" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X29" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y29" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z29" s="49"/>
-      <c r="AA29" s="49"/>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="49">
-        <v>1177943</v>
-      </c>
-      <c r="C30" s="49" t="s">
-        <v>455</v>
-      </c>
-      <c r="D30" s="49" t="s">
-        <v>456</v>
-      </c>
-      <c r="E30" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F30" s="50" t="s">
-        <v>457</v>
-      </c>
-      <c r="G30" s="51">
-        <v>21</v>
-      </c>
-      <c r="H30" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I30" s="51">
-        <v>126.28594991999999</v>
-      </c>
-      <c r="J30" s="52">
-        <v>9.9347496599633475E-2</v>
-      </c>
-      <c r="K30" s="49"/>
-      <c r="L30" s="51">
-        <v>126.28594991999999</v>
-      </c>
-      <c r="M30" s="51">
-        <v>4.3475317599999999</v>
-      </c>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="52">
-        <v>3.4426092235550251E-2</v>
-      </c>
-      <c r="Q30" s="51">
-        <v>4.3475317599999999</v>
-      </c>
-      <c r="R30" s="51">
-        <v>0.1125</v>
-      </c>
-      <c r="S30" s="51">
-        <v>3.2669999999999999</v>
-      </c>
-      <c r="T30" s="51">
-        <v>4.1327999999999996</v>
-      </c>
-      <c r="U30" s="52">
-        <v>3.3923876378405098E-2</v>
-      </c>
-      <c r="V30" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W30" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X30" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y30" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z30" s="49"/>
-      <c r="AA30" s="49"/>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="49">
-        <v>3391652</v>
-      </c>
-      <c r="C31" s="49" t="s">
-        <v>458</v>
-      </c>
-      <c r="D31" s="49" t="s">
-        <v>459</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>460</v>
-      </c>
-      <c r="G31" s="51">
-        <v>7883</v>
-      </c>
-      <c r="H31" s="49" t="s">
-        <v>394</v>
-      </c>
-      <c r="I31" s="51">
-        <v>1721.3053353600001</v>
-      </c>
-      <c r="J31" s="52">
-        <v>-7.389413157301894E-2</v>
-      </c>
-      <c r="K31" s="49"/>
-      <c r="L31" s="51">
-        <v>1721.3053353600001</v>
-      </c>
-      <c r="M31" s="51">
-        <v>59.852915200000012</v>
-      </c>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="52">
-        <v>3.477181762611696E-2</v>
-      </c>
-      <c r="Q31" s="51">
-        <v>59.852915200000012</v>
-      </c>
-      <c r="R31" s="51">
-        <v>0.1779</v>
-      </c>
-      <c r="S31" s="51">
-        <v>5.1162000000000001</v>
-      </c>
-      <c r="T31" s="51">
-        <v>8.3924000000000003</v>
-      </c>
-      <c r="U31" s="52">
-        <v>5.3291056417545501E-2</v>
-      </c>
-      <c r="V31" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="W31" s="49">
-        <v>2025</v>
-      </c>
-      <c r="X31" s="49">
-        <v>2025</v>
-      </c>
-      <c r="Y31" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z31" s="49"/>
-      <c r="AA31" s="49"/>
+      <c r="I40" s="45">
+        <v>373.12951199999998</v>
+      </c>
+      <c r="J40" s="48">
+        <v>1.9376030661461211E-2</v>
+      </c>
+      <c r="K40" s="64">
+        <f>I40*P40</f>
+        <v>1488.8613787823999</v>
+      </c>
+      <c r="L40" s="47">
+        <v>373.12951199999998</v>
+      </c>
+      <c r="M40" s="45">
+        <v>112.13277600000001</v>
+      </c>
+      <c r="N40" s="48">
+        <v>0.30051971874044642</v>
+      </c>
+      <c r="O40" s="45">
+        <v>112.13277600000001</v>
+      </c>
+      <c r="P40" s="45">
+        <v>3.9902000000000002</v>
+      </c>
+      <c r="Q40" s="45">
+        <v>13.277699999999999</v>
+      </c>
+      <c r="R40" s="45">
+        <v>16.438199999999998</v>
+      </c>
+      <c r="S40" s="48">
+        <v>-2.3341908380170581E-2</v>
+      </c>
+      <c r="T40" s="45">
+        <v>3.8904999999999998</v>
+      </c>
+      <c r="U40" s="45">
+        <v>2.9639000000000002</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{3FCDA843-863C-49DA-8D69-65248E9BAD46}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{A6C3D4D7-5666-461C-8F00-4AFABB7815A0}"/>
-    <hyperlink ref="F6" r:id="rId3" xr:uid="{4E311B2E-5466-407D-A6E4-B1F2E12CE06A}"/>
-    <hyperlink ref="F7" r:id="rId4" xr:uid="{E904097C-7559-4657-94BD-33F8D28AC1A9}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{12257223-6B9E-4DE6-B485-B6C665BD7A01}"/>
-    <hyperlink ref="F9" r:id="rId6" xr:uid="{D9EADDC5-E22C-4FEF-B278-ACF15DFA7A26}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{A01FAD40-572B-4A43-A38A-E0D27FC5C465}"/>
-    <hyperlink ref="F31" r:id="rId8" xr:uid="{297DC890-B5BA-4B02-8420-A197E86C0EBA}"/>
-    <hyperlink ref="F11" r:id="rId9" xr:uid="{485701F7-B818-4C5A-A466-C6101859DE5A}"/>
-    <hyperlink ref="F12" r:id="rId10" xr:uid="{BF86C56E-A219-4902-80F3-9A89180FA768}"/>
-    <hyperlink ref="F28" r:id="rId11" xr:uid="{F0907989-89D9-4426-9200-63339073E4BA}"/>
-    <hyperlink ref="F13" r:id="rId12" xr:uid="{F9C20E58-8D82-4EF0-BE7E-32D10DD8F11E}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{9CE7DFB8-A189-46E1-8D87-6A1CA75273A8}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{76DBCEAC-7B03-40A6-B18F-7A72B13A6529}"/>
-    <hyperlink ref="F29" r:id="rId15" xr:uid="{DFD85D45-536E-4FE4-80ED-1BF4901562DC}"/>
-    <hyperlink ref="F16" r:id="rId16" xr:uid="{84681402-07BC-45CE-BE88-A680E33945FA}"/>
-    <hyperlink ref="F17" r:id="rId17" xr:uid="{156C775B-3BE9-4128-8CA0-F00203755FC0}"/>
-    <hyperlink ref="F25" r:id="rId18" xr:uid="{6593144B-1E23-4954-B832-4B6609C0E55C}"/>
-    <hyperlink ref="F26" r:id="rId19" xr:uid="{03304E9C-E905-45AF-A9F5-29F269CBC59E}"/>
-    <hyperlink ref="F27" r:id="rId20" xr:uid="{EBAB0365-9B09-4E9B-A417-97E1EC17F8B2}"/>
-    <hyperlink ref="F30" r:id="rId21" xr:uid="{D1978D21-A344-4473-A5D9-4379F07EF08F}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{444FBF66-89E0-44A5-AF63-7B11B8B2225A}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{2520F3BD-2D84-4C16-872A-B805AEA571F3}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{E4D4E574-8C0C-460F-9A71-F7CDA5F55449}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{9825DAED-A7D7-4CD8-A999-92B9897F08AD}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{45DFA1A8-11AB-4E46-90EB-D5A11DEE625D}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{0F19311C-737B-49AD-9090-37CF0AC26AB4}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{489EF4F5-96E5-4F01-B58C-1E7275C7AB7A}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{B121F2F1-DFCB-42B9-A300-4AB78D8F843F}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{E99B79C3-D20A-4FB7-AB29-BE5C99D148D6}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{28A51268-5373-4AD0-9FBD-F6F1F92205C8}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{81D273CD-4A9F-4F5C-8830-0E228677DA4A}"/>
+    <hyperlink ref="F14" r:id="rId12" xr:uid="{59E8AB2F-D5A3-4F24-84C2-8FDC0F79C7BD}"/>
+    <hyperlink ref="F15" r:id="rId13" xr:uid="{A466BB7A-9E7B-4161-B0AD-51ABBF74BA34}"/>
+    <hyperlink ref="F28" r:id="rId14" xr:uid="{094A7469-6EFB-48E7-AE5A-7AFB9FB3BB0C}"/>
+    <hyperlink ref="F29" r:id="rId15" xr:uid="{D9A865D0-5450-495E-B00E-9E689DF8785E}"/>
+    <hyperlink ref="F30" r:id="rId16" xr:uid="{46BD100D-E376-4FC0-B81F-1F3082D08462}"/>
+    <hyperlink ref="F32" r:id="rId17" xr:uid="{9ABBD1D5-EB8F-4FFB-AFC9-367F197C476F}"/>
+    <hyperlink ref="F33" r:id="rId18" xr:uid="{C1A650BB-75C2-46F6-A20A-5C645D8857B4}"/>
+    <hyperlink ref="F34" r:id="rId19" xr:uid="{70DCDBA8-4D6C-4094-8C21-262F246C9B49}"/>
+    <hyperlink ref="F35" r:id="rId20" xr:uid="{CD51AE47-DCB6-4DA3-A46C-8C3C72ADD0DA}"/>
+    <hyperlink ref="F36" r:id="rId21" xr:uid="{0344AD9D-BD24-44E8-B4AF-224AD2B8B0A5}"/>
+    <hyperlink ref="F37" r:id="rId22" xr:uid="{71DF218A-F55F-4D6A-8821-E6BAF9BDB475}"/>
+    <hyperlink ref="F38" r:id="rId23" xr:uid="{8FC6DF4C-66BF-4D7C-BF93-E70C21A55CFE}"/>
+    <hyperlink ref="F39" r:id="rId24" xr:uid="{54228C33-2F2E-4D2C-9956-21A5FCD8EADD}"/>
+    <hyperlink ref="F40" r:id="rId25" xr:uid="{B39E81AD-E462-49E1-923C-4DC792BB2CA1}"/>
+    <hyperlink ref="F16" r:id="rId26" xr:uid="{5C2D824F-695A-4CCD-89DB-AAB419A3B9FC}"/>
+    <hyperlink ref="F17" r:id="rId27" xr:uid="{F3454F3E-7AD4-4B14-A740-765993EE8694}"/>
+    <hyperlink ref="F18" r:id="rId28" xr:uid="{75377B02-5756-4735-9598-8457AA31CC60}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
